--- a/revampData/EXPORTED_METRICS/Control18SNF_CJM_PPCS_Battery_11172021.xlsx
+++ b/revampData/EXPORTED_METRICS/Control18SNF_CJM_PPCS_Battery_11172021.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="589" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="591" uniqueCount="83">
   <si>
     <t>SubjectID</t>
   </si>
@@ -21,10 +21,10 @@
     <t>Control18SNF</t>
   </si>
   <si>
-    <t>StudyName</t>
+    <t>Study_Name</t>
   </si>
   <si>
-    <t>PPCSBattery</t>
+    <t>PPCS_Battery</t>
   </si>
   <si>
     <t>Movement</t>
@@ -102,160 +102,166 @@
     <t>R5_L5_SACC</t>
   </si>
   <si>
-    <t>MovementIndex</t>
+    <t>Movement_Index</t>
   </si>
   <si>
-    <t>LeftEyeRSI</t>
+    <t>Left_Eye_RSI</t>
   </si>
   <si>
-    <t>LeftEyeREI</t>
+    <t>Left_Eye_REI</t>
   </si>
   <si>
-    <t>LeftEyeRA</t>
+    <t>Left_Eye_RA</t>
   </si>
   <si>
-    <t>LeftEyePVI</t>
+    <t>Left_Eye_PVI</t>
   </si>
   <si>
-    <t>LeftEyePV</t>
+    <t>Left_Eye_PV</t>
   </si>
   <si>
-    <t>LeftEyeFA</t>
+    <t>Left_Eye_FA</t>
   </si>
   <si>
-    <t>LeftEyeRSID</t>
+    <t>Left_Eye_RSID</t>
   </si>
   <si>
-    <t>LeftEyeREID</t>
+    <t>Left_Eye_REID</t>
   </si>
   <si>
-    <t>LeftEyeRAD</t>
+    <t>Left_Eye_RAD</t>
   </si>
   <si>
-    <t>LeftEyePDROCI</t>
+    <t>Left_Eye_PDROCI</t>
   </si>
   <si>
-    <t>LeftEyePDROC</t>
+    <t>Left_Eye_PDROC</t>
   </si>
   <si>
-    <t>LeftEyeFD</t>
+    <t>Left_Eye_FD</t>
   </si>
   <si>
-    <t>LeftEyeID</t>
+    <t>Left_Eye_ID</t>
   </si>
   <si>
-    <t>LeftEyeHClass</t>
+    <t>Left_Eye_HClass</t>
   </si>
   <si>
-    <t>LeftEyeVClass</t>
+    <t>Left_Eye_VClass</t>
   </si>
   <si>
-    <t>LeftEyePClass</t>
+    <t>Left_Eye_PClass</t>
   </si>
   <si>
-    <t>LeftEyeComments</t>
+    <t>Left_Eye_Comments</t>
   </si>
   <si>
-    <t>RightEyeRSI</t>
+    <t>Right_Eye_RSI</t>
   </si>
   <si>
-    <t>RightEyeREI</t>
+    <t>Right_Eye_REI</t>
   </si>
   <si>
-    <t>RightEyeRA</t>
+    <t>Right_Eye_RA</t>
   </si>
   <si>
-    <t>RightEyePVI</t>
+    <t>Right_Eye_PVI</t>
   </si>
   <si>
-    <t>RightEyePV</t>
+    <t>Right_Eye_PV</t>
   </si>
   <si>
-    <t>RightEyeFA</t>
+    <t>Right_Eye_FA</t>
   </si>
   <si>
-    <t>RightEyeRSID</t>
+    <t>Right_Eye_RSID</t>
   </si>
   <si>
-    <t>RightEyeREID</t>
+    <t>Right_Eye_REID</t>
   </si>
   <si>
-    <t>RightEyeRAD</t>
+    <t>Right_Eye_RAD</t>
   </si>
   <si>
-    <t>RightEyePDROCI</t>
+    <t>Right_Eye_PDROCI</t>
   </si>
   <si>
-    <t>RightEyePDROC</t>
+    <t>Right_Eye_PDROC</t>
   </si>
   <si>
-    <t>RightEyeFD</t>
+    <t>Right_Eye_FD</t>
   </si>
   <si>
-    <t>RightEyeID</t>
+    <t>Right_Eye_ID</t>
   </si>
   <si>
-    <t>RightEyeHClass</t>
+    <t>Right_Eye_HClass</t>
   </si>
   <si>
-    <t>RightEyeVClass</t>
+    <t>Right_Eye_VClass</t>
   </si>
   <si>
-    <t>RightEyePClass</t>
+    <t>Right_Eye_PClass</t>
   </si>
   <si>
-    <t>RightEyeComments</t>
+    <t>Right_Eye_Comments</t>
   </si>
   <si>
-    <t>CombinedRSI</t>
+    <t>Combined_RSI</t>
   </si>
   <si>
-    <t>CombinedREI</t>
+    <t>Combined_REI</t>
   </si>
   <si>
-    <t>CombinedRA</t>
+    <t>Combined_RA</t>
   </si>
   <si>
-    <t>CombinedPVI</t>
+    <t>Combined_PVI</t>
   </si>
   <si>
-    <t>CombinedPV</t>
+    <t>Combined_PV</t>
   </si>
   <si>
-    <t>CombinedFA</t>
+    <t>Combined_FA</t>
   </si>
   <si>
-    <t>CombinedRSID</t>
+    <t>Combined_RSID</t>
   </si>
   <si>
-    <t>CombinedREID</t>
+    <t>Combined_REID</t>
   </si>
   <si>
-    <t>CombinedRAD</t>
+    <t>Combined_RAD</t>
   </si>
   <si>
-    <t>CombinedPDROCI</t>
+    <t>Combined_PDROCI</t>
   </si>
   <si>
-    <t>CombinedPDROC</t>
+    <t>Combined_PDROC</t>
   </si>
   <si>
-    <t>CombinedFD</t>
+    <t>Combined_FD</t>
   </si>
   <si>
-    <t>CombinedID</t>
+    <t>Combined_ID</t>
   </si>
   <si>
-    <t>CombinedHClass</t>
+    <t>Combined_HClass</t>
   </si>
   <si>
-    <t>CombinedVClass</t>
+    <t>Combined_VClass</t>
   </si>
   <si>
-    <t>CombinedPClass</t>
+    <t>Combined_PClass</t>
   </si>
   <si>
-    <t>CombinedComments</t>
+    <t>Combined_Comments</t>
+  </si>
+  <si>
+    <t>Blink_In_Transient</t>
+  </si>
+  <si>
+    <t>Blink_Count</t>
   </si>
 </sst>
 </file>
@@ -301,64 +307,66 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BC179"/>
+  <dimension ref="A1:BE179"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.140625" customWidth="true"/>
-    <col min="2" max="2" width="12" customWidth="true"/>
+    <col min="2" max="2" width="13" customWidth="true"/>
     <col min="3" max="3" width="23.140625" customWidth="true"/>
-    <col min="4" max="4" width="15.85546875" customWidth="true"/>
-    <col min="5" max="5" width="10.42578125" customWidth="true"/>
-    <col min="6" max="6" width="10.42578125" customWidth="true"/>
-    <col min="7" max="7" width="13.7109375" customWidth="true"/>
-    <col min="8" max="8" width="10.7109375" customWidth="true"/>
-    <col min="9" max="9" width="13.42578125" customWidth="true"/>
-    <col min="10" max="10" width="10" customWidth="true"/>
-    <col min="11" max="11" width="11.7109375" customWidth="true"/>
-    <col min="12" max="12" width="11.7109375" customWidth="true"/>
-    <col min="13" max="13" width="15.42578125" customWidth="true"/>
-    <col min="14" max="14" width="14.42578125" customWidth="true"/>
-    <col min="15" max="15" width="15.42578125" customWidth="true"/>
-    <col min="16" max="16" width="10" customWidth="true"/>
-    <col min="17" max="17" width="9.5703125" customWidth="true"/>
-    <col min="18" max="18" width="13.42578125" customWidth="true"/>
-    <col min="19" max="19" width="13.42578125" customWidth="true"/>
-    <col min="20" max="20" width="13.28515625" customWidth="true"/>
-    <col min="21" max="21" width="17.28515625" customWidth="true"/>
-    <col min="22" max="22" width="11.5703125" customWidth="true"/>
-    <col min="23" max="23" width="11.5703125" customWidth="true"/>
-    <col min="24" max="24" width="14.42578125" customWidth="true"/>
-    <col min="25" max="25" width="11.85546875" customWidth="true"/>
-    <col min="26" max="26" width="13.42578125" customWidth="true"/>
-    <col min="27" max="27" width="11.140625" customWidth="true"/>
-    <col min="28" max="28" width="12.85546875" customWidth="true"/>
-    <col min="29" max="29" width="12.85546875" customWidth="true"/>
-    <col min="30" max="30" width="15.42578125" customWidth="true"/>
-    <col min="31" max="31" width="15.5703125" customWidth="true"/>
-    <col min="32" max="32" width="15.42578125" customWidth="true"/>
-    <col min="33" max="33" width="11.140625" customWidth="true"/>
-    <col min="34" max="34" width="10.7109375" customWidth="true"/>
-    <col min="35" max="35" width="14.5703125" customWidth="true"/>
-    <col min="36" max="36" width="14.5703125" customWidth="true"/>
-    <col min="37" max="37" width="14.42578125" customWidth="true"/>
-    <col min="38" max="38" width="18.42578125" customWidth="true"/>
-    <col min="39" max="39" width="13" customWidth="true"/>
-    <col min="40" max="40" width="13" customWidth="true"/>
-    <col min="41" max="41" width="14.42578125" customWidth="true"/>
-    <col min="42" max="42" width="13.28515625" customWidth="true"/>
-    <col min="43" max="43" width="13.42578125" customWidth="true"/>
-    <col min="44" max="44" width="12.5703125" customWidth="true"/>
-    <col min="45" max="45" width="14.28515625" customWidth="true"/>
-    <col min="46" max="46" width="14.28515625" customWidth="true"/>
-    <col min="47" max="47" width="15.7109375" customWidth="true"/>
-    <col min="48" max="48" width="17" customWidth="true"/>
-    <col min="49" max="49" width="16.42578125" customWidth="true"/>
-    <col min="50" max="50" width="12.5703125" customWidth="true"/>
-    <col min="51" max="51" width="12.140625" customWidth="true"/>
-    <col min="52" max="52" width="16" customWidth="true"/>
-    <col min="53" max="53" width="16" customWidth="true"/>
-    <col min="54" max="54" width="15.85546875" customWidth="true"/>
-    <col min="55" max="55" width="19.85546875" customWidth="true"/>
+    <col min="4" max="4" width="16.85546875" customWidth="true"/>
+    <col min="5" max="5" width="12.42578125" customWidth="true"/>
+    <col min="6" max="6" width="12.42578125" customWidth="true"/>
+    <col min="7" max="7" width="12.140625" customWidth="true"/>
+    <col min="8" max="8" width="12.7109375" customWidth="true"/>
+    <col min="9" max="9" width="12.140625" customWidth="true"/>
+    <col min="10" max="10" width="12" customWidth="true"/>
+    <col min="11" max="11" width="13.7109375" customWidth="true"/>
+    <col min="12" max="12" width="13.7109375" customWidth="true"/>
+    <col min="13" max="13" width="13.42578125" customWidth="true"/>
+    <col min="14" max="14" width="16.42578125" customWidth="true"/>
+    <col min="15" max="15" width="15.85546875" customWidth="true"/>
+    <col min="16" max="16" width="12" customWidth="true"/>
+    <col min="17" max="17" width="11.5703125" customWidth="true"/>
+    <col min="18" max="18" width="15.42578125" customWidth="true"/>
+    <col min="19" max="19" width="15.42578125" customWidth="true"/>
+    <col min="20" max="20" width="15.28515625" customWidth="true"/>
+    <col min="21" max="21" width="19.28515625" customWidth="true"/>
+    <col min="22" max="22" width="13.5703125" customWidth="true"/>
+    <col min="23" max="23" width="13.5703125" customWidth="true"/>
+    <col min="24" max="24" width="13.28515625" customWidth="true"/>
+    <col min="25" max="25" width="13.85546875" customWidth="true"/>
+    <col min="26" max="26" width="13.28515625" customWidth="true"/>
+    <col min="27" max="27" width="13.140625" customWidth="true"/>
+    <col min="28" max="28" width="14.85546875" customWidth="true"/>
+    <col min="29" max="29" width="14.85546875" customWidth="true"/>
+    <col min="30" max="30" width="14.5703125" customWidth="true"/>
+    <col min="31" max="31" width="17.5703125" customWidth="true"/>
+    <col min="32" max="32" width="17" customWidth="true"/>
+    <col min="33" max="33" width="13.140625" customWidth="true"/>
+    <col min="34" max="34" width="12.7109375" customWidth="true"/>
+    <col min="35" max="35" width="16.5703125" customWidth="true"/>
+    <col min="36" max="36" width="16.5703125" customWidth="true"/>
+    <col min="37" max="37" width="16.42578125" customWidth="true"/>
+    <col min="38" max="38" width="20.42578125" customWidth="true"/>
+    <col min="39" max="39" width="14" customWidth="true"/>
+    <col min="40" max="40" width="14" customWidth="true"/>
+    <col min="41" max="41" width="13.7109375" customWidth="true"/>
+    <col min="42" max="42" width="14.28515625" customWidth="true"/>
+    <col min="43" max="43" width="13.7109375" customWidth="true"/>
+    <col min="44" max="44" width="13.5703125" customWidth="true"/>
+    <col min="45" max="45" width="15.28515625" customWidth="true"/>
+    <col min="46" max="46" width="15.28515625" customWidth="true"/>
+    <col min="47" max="47" width="15" customWidth="true"/>
+    <col min="48" max="48" width="18" customWidth="true"/>
+    <col min="49" max="49" width="17.42578125" customWidth="true"/>
+    <col min="50" max="50" width="13.5703125" customWidth="true"/>
+    <col min="51" max="51" width="13.140625" customWidth="true"/>
+    <col min="52" max="52" width="17" customWidth="true"/>
+    <col min="53" max="53" width="17" customWidth="true"/>
+    <col min="54" max="54" width="16.85546875" customWidth="true"/>
+    <col min="55" max="55" width="20.85546875" customWidth="true"/>
+    <col min="56" max="56" width="17.5703125" customWidth="true"/>
+    <col min="57" max="57" width="11.85546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -527,6 +535,12 @@
       <c r="BC1" s="0" t="s">
         <v>80</v>
       </c>
+      <c r="BD1" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="BE1" s="0" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
@@ -541,153 +555,65 @@
       <c r="D2" s="0">
         <v>1</v>
       </c>
-      <c r="E2" s="0">
-        <v>0.23799999999999999</v>
-      </c>
-      <c r="F2" s="0">
-        <v>0.81799999999999995</v>
-      </c>
-      <c r="G2" s="0">
-        <v>0.083662354077084028</v>
-      </c>
-      <c r="H2" s="0">
-        <v>0.55200000000000005</v>
-      </c>
-      <c r="I2" s="0">
-        <v>0</v>
-      </c>
-      <c r="J2" s="0">
-        <v>0.085999999999999993</v>
-      </c>
-      <c r="K2" s="0">
-        <v>0.27200000000000002</v>
-      </c>
-      <c r="L2" s="0">
-        <v>0.73999999999999999</v>
-      </c>
-      <c r="M2" s="0">
-        <v>0.00021695678400749611</v>
-      </c>
-      <c r="N2" s="0">
-        <v>0.496</v>
-      </c>
-      <c r="O2" s="0">
-        <v>0</v>
-      </c>
-      <c r="P2" s="0">
-        <v>0.001</v>
-      </c>
-      <c r="Q2" s="0">
-        <v>0</v>
-      </c>
-      <c r="R2" s="0">
-        <v>1</v>
-      </c>
-      <c r="S2" s="0">
-        <v>1</v>
-      </c>
-      <c r="T2" s="0">
-        <v>0</v>
-      </c>
+      <c r="E2" s="0"/>
+      <c r="F2" s="0"/>
+      <c r="G2" s="0"/>
+      <c r="H2" s="0"/>
+      <c r="I2" s="0"/>
+      <c r="J2" s="0"/>
+      <c r="K2" s="0"/>
+      <c r="L2" s="0"/>
+      <c r="M2" s="0"/>
+      <c r="N2" s="0"/>
+      <c r="O2" s="0"/>
+      <c r="P2" s="0"/>
+      <c r="Q2" s="0"/>
+      <c r="R2" s="0"/>
+      <c r="S2" s="0"/>
+      <c r="T2" s="0"/>
       <c r="U2" s="0"/>
-      <c r="V2" s="0">
-        <v>0.216</v>
-      </c>
-      <c r="W2" s="0">
-        <v>0.70199999999999996</v>
-      </c>
-      <c r="X2" s="0">
-        <v>0.073777533565538844</v>
-      </c>
-      <c r="Y2" s="0">
-        <v>0.48799999999999999</v>
-      </c>
-      <c r="Z2" s="0">
-        <v>0.27815780772099885</v>
-      </c>
-      <c r="AA2" s="0">
-        <v>-0.17100000000000001</v>
-      </c>
-      <c r="AB2" s="0">
-        <v>0.38</v>
-      </c>
-      <c r="AC2" s="0">
-        <v>0.91200000000000003</v>
-      </c>
-      <c r="AD2" s="0">
-        <v>-0.0024869487544203301</v>
-      </c>
-      <c r="AE2" s="0">
-        <v>0.64200000000000002</v>
-      </c>
-      <c r="AF2" s="0">
-        <v>0.0022634210433272618</v>
-      </c>
-      <c r="AG2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AH2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AI2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AJ2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AK2" s="0">
-        <v>0</v>
-      </c>
+      <c r="V2" s="0"/>
+      <c r="W2" s="0"/>
+      <c r="X2" s="0"/>
+      <c r="Y2" s="0"/>
+      <c r="Z2" s="0"/>
+      <c r="AA2" s="0"/>
+      <c r="AB2" s="0"/>
+      <c r="AC2" s="0"/>
+      <c r="AD2" s="0"/>
+      <c r="AE2" s="0"/>
+      <c r="AF2" s="0"/>
+      <c r="AG2" s="0"/>
+      <c r="AH2" s="0"/>
+      <c r="AI2" s="0"/>
+      <c r="AJ2" s="0"/>
+      <c r="AK2" s="0"/>
       <c r="AL2" s="0"/>
-      <c r="AM2" s="0">
-        <v>0.21199999999999999</v>
-      </c>
-      <c r="AN2" s="0">
-        <v>0.61599999999999999</v>
-      </c>
-      <c r="AO2" s="0">
-        <v>1.1385153335661997</v>
-      </c>
-      <c r="AP2" s="0">
-        <v>0.40600000000000003</v>
-      </c>
-      <c r="AQ2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AR2" s="0">
-        <v>-0.29999999999999999</v>
-      </c>
-      <c r="AS2" s="0">
-        <v>0.24199999999999999</v>
-      </c>
-      <c r="AT2" s="0">
-        <v>0.82199999999999995</v>
-      </c>
-      <c r="AU2" s="0">
-        <v>-0.0026534887907593251</v>
-      </c>
-      <c r="AV2" s="0">
-        <v>0.504</v>
-      </c>
-      <c r="AW2" s="0">
-        <v>0.0067817257994531189</v>
-      </c>
-      <c r="AX2" s="0">
-        <v>0</v>
-      </c>
-      <c r="AY2" s="0">
-        <v>0</v>
-      </c>
+      <c r="AM2" s="0"/>
+      <c r="AN2" s="0"/>
+      <c r="AO2" s="0"/>
+      <c r="AP2" s="0"/>
+      <c r="AQ2" s="0"/>
+      <c r="AR2" s="0"/>
+      <c r="AS2" s="0"/>
+      <c r="AT2" s="0"/>
+      <c r="AU2" s="0"/>
+      <c r="AV2" s="0"/>
+      <c r="AW2" s="0"/>
+      <c r="AX2" s="0"/>
+      <c r="AY2" s="0"/>
       <c r="AZ2" s="0">
-        <v>1</v>
-      </c>
-      <c r="BA2" s="0">
-        <v>1</v>
-      </c>
-      <c r="BB2" s="0">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="BA2" s="0"/>
+      <c r="BB2" s="0"/>
       <c r="BC2" s="0"/>
+      <c r="BD2" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE2" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
@@ -702,153 +628,75 @@
       <c r="D3" s="0">
         <v>2</v>
       </c>
-      <c r="E3" s="0">
-        <v>0.17399999999999999</v>
-      </c>
-      <c r="F3" s="0">
-        <v>1.468</v>
-      </c>
-      <c r="G3" s="0">
-        <v>-4.6938628904098643</v>
-      </c>
-      <c r="H3" s="0">
-        <v>0.96399999999999997</v>
-      </c>
-      <c r="I3" s="0">
-        <v>-0.25380750467807189</v>
-      </c>
-      <c r="J3" s="0">
-        <v>-4.6500000000000004</v>
-      </c>
-      <c r="K3" s="0">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="L3" s="0">
-        <v>0.84799999999999998</v>
-      </c>
-      <c r="M3" s="0">
-        <v>-0.0056632127945866291</v>
-      </c>
-      <c r="N3" s="0">
-        <v>0.34000000000000002</v>
-      </c>
-      <c r="O3" s="0">
-        <v>-0.012027533791246405</v>
-      </c>
-      <c r="P3" s="0">
-        <v>-0.0040000000000000001</v>
-      </c>
-      <c r="Q3" s="0">
-        <v>0</v>
-      </c>
-      <c r="R3" s="0">
-        <v>0</v>
-      </c>
-      <c r="S3" s="0">
-        <v>1</v>
-      </c>
-      <c r="T3" s="0">
-        <v>0</v>
-      </c>
+      <c r="E3" s="0"/>
+      <c r="F3" s="0"/>
+      <c r="G3" s="0"/>
+      <c r="H3" s="0"/>
+      <c r="I3" s="0"/>
+      <c r="J3" s="0"/>
+      <c r="K3" s="0"/>
+      <c r="L3" s="0"/>
+      <c r="M3" s="0"/>
+      <c r="N3" s="0"/>
+      <c r="O3" s="0"/>
+      <c r="P3" s="0"/>
+      <c r="Q3" s="0"/>
+      <c r="R3" s="0"/>
+      <c r="S3" s="0"/>
+      <c r="T3" s="0"/>
       <c r="U3" s="0"/>
-      <c r="V3" s="0">
-        <v>0.096000000000000002</v>
-      </c>
-      <c r="W3" s="0">
-        <v>0.81399999999999995</v>
-      </c>
-      <c r="X3" s="0">
-        <v>-5.2753870431202889</v>
-      </c>
-      <c r="Y3" s="0">
-        <v>0.42199999999999999</v>
-      </c>
-      <c r="Z3" s="0">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="0">
-        <v>-5.0999999999999996</v>
-      </c>
-      <c r="AB3" s="0">
-        <v>0.61599999999999999</v>
-      </c>
-      <c r="AC3" s="0">
-        <v>1.468</v>
-      </c>
-      <c r="AD3" s="0">
-        <v>-0.0028590015391689607</v>
-      </c>
-      <c r="AE3" s="0">
-        <v>0.96799999999999997</v>
-      </c>
-      <c r="AF3" s="0">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="0">
-        <v>-0.0040000000000000001</v>
-      </c>
-      <c r="AH3" s="0">
-        <v>-0</v>
-      </c>
-      <c r="AI3" s="0">
-        <v>0</v>
-      </c>
-      <c r="AJ3" s="0">
-        <v>1</v>
-      </c>
-      <c r="AK3" s="0">
-        <v>0</v>
-      </c>
+      <c r="V3" s="0"/>
+      <c r="W3" s="0"/>
+      <c r="X3" s="0"/>
+      <c r="Y3" s="0"/>
+      <c r="Z3" s="0"/>
+      <c r="AA3" s="0"/>
+      <c r="AB3" s="0"/>
+      <c r="AC3" s="0"/>
+      <c r="AD3" s="0"/>
+      <c r="AE3" s="0"/>
+      <c r="AF3" s="0"/>
+      <c r="AG3" s="0"/>
+      <c r="AH3" s="0"/>
+      <c r="AI3" s="0"/>
+      <c r="AJ3" s="0"/>
+      <c r="AK3" s="0"/>
       <c r="AL3" s="0"/>
       <c r="AM3" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.14599999999999999</v>
       </c>
       <c r="AN3" s="0">
-        <v>1.3740000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="AO3" s="0">
-        <v>-5.2983465111836381</v>
+        <v>-4.6465090794734287</v>
       </c>
       <c r="AP3" s="0">
-        <v>0.73999999999999999</v>
+        <v>0.24399999999999999</v>
       </c>
       <c r="AQ3" s="0">
-        <v>-0.6613708272440455</v>
+        <v>-82.103405908622534</v>
       </c>
       <c r="AR3" s="0">
-        <v>-5.0999999999999996</v>
-      </c>
-      <c r="AS3" s="0">
-        <v>0.33200000000000002</v>
-      </c>
-      <c r="AT3" s="0">
-        <v>1.248</v>
-      </c>
-      <c r="AU3" s="0">
-        <v>-0.0067709950037896649</v>
-      </c>
-      <c r="AV3" s="0">
-        <v>0.87</v>
-      </c>
-      <c r="AW3" s="0">
-        <v>-0.021125903431188676</v>
-      </c>
-      <c r="AX3" s="0">
-        <v>-0.0040000000000000001</v>
-      </c>
-      <c r="AY3" s="0">
-        <v>-0</v>
-      </c>
-      <c r="AZ3" s="0">
-        <v>1</v>
-      </c>
-      <c r="BA3" s="0">
-        <v>0</v>
-      </c>
-      <c r="BB3" s="0">
-        <v>0</v>
-      </c>
+        <v>-4.8739999999999997</v>
+      </c>
+      <c r="AS3" s="0"/>
+      <c r="AT3" s="0"/>
+      <c r="AU3" s="0"/>
+      <c r="AV3" s="0"/>
+      <c r="AW3" s="0"/>
+      <c r="AX3" s="0"/>
+      <c r="AY3" s="0"/>
+      <c r="AZ3" s="0"/>
+      <c r="BA3" s="0"/>
+      <c r="BB3" s="0"/>
       <c r="BC3" s="0"/>
+      <c r="BD3" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE3" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
@@ -863,153 +711,63 @@
       <c r="D4" s="0">
         <v>3</v>
       </c>
-      <c r="E4" s="0">
-        <v>0.25800000000000001</v>
-      </c>
-      <c r="F4" s="0">
-        <v>0.89600000000000002</v>
-      </c>
-      <c r="G4" s="0">
-        <v>-0.94823727167550631</v>
-      </c>
-      <c r="H4" s="0">
-        <v>0.51000000000000001</v>
-      </c>
-      <c r="I4" s="0">
-        <v>-0.88321219802445228</v>
-      </c>
-      <c r="J4" s="0">
-        <v>-4.8440000000000003</v>
-      </c>
-      <c r="K4" s="0">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="L4" s="0">
-        <v>0.77200000000000002</v>
-      </c>
-      <c r="M4" s="0">
-        <v>-0.0055323634828677607</v>
-      </c>
-      <c r="N4" s="0">
-        <v>0.49399999999999999</v>
-      </c>
-      <c r="O4" s="0">
-        <v>0</v>
-      </c>
-      <c r="P4" s="0">
-        <v>0.0030000000000000001</v>
-      </c>
-      <c r="Q4" s="0">
-        <v>-0</v>
-      </c>
-      <c r="R4" s="0">
-        <v>1</v>
-      </c>
-      <c r="S4" s="0">
-        <v>1</v>
-      </c>
-      <c r="T4" s="0">
-        <v>1</v>
-      </c>
+      <c r="E4" s="0"/>
+      <c r="F4" s="0"/>
+      <c r="G4" s="0"/>
+      <c r="H4" s="0"/>
+      <c r="I4" s="0"/>
+      <c r="J4" s="0"/>
+      <c r="K4" s="0"/>
+      <c r="L4" s="0"/>
+      <c r="M4" s="0"/>
+      <c r="N4" s="0"/>
+      <c r="O4" s="0"/>
+      <c r="P4" s="0"/>
+      <c r="Q4" s="0"/>
+      <c r="R4" s="0"/>
+      <c r="S4" s="0"/>
+      <c r="T4" s="0"/>
       <c r="U4" s="0"/>
-      <c r="V4" s="0">
-        <v>0.28399999999999997</v>
-      </c>
-      <c r="W4" s="0">
-        <v>0.71999999999999997</v>
-      </c>
-      <c r="X4" s="0">
-        <v>-0.92376022762363874</v>
-      </c>
-      <c r="Y4" s="0">
-        <v>0.53200000000000003</v>
-      </c>
-      <c r="Z4" s="0">
-        <v>-0.51156858044709708</v>
-      </c>
-      <c r="AA4" s="0">
-        <v>-5.3559999999999999</v>
-      </c>
-      <c r="AB4" s="0">
-        <v>0.156</v>
-      </c>
-      <c r="AC4" s="0">
-        <v>0.68600000000000005</v>
-      </c>
-      <c r="AD4" s="0">
-        <v>-0.0054587062323674732</v>
-      </c>
-      <c r="AE4" s="0">
-        <v>0.438</v>
-      </c>
-      <c r="AF4" s="0">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="0">
-        <v>0.002</v>
-      </c>
-      <c r="AH4" s="0">
-        <v>0</v>
-      </c>
-      <c r="AI4" s="0">
-        <v>1</v>
-      </c>
-      <c r="AJ4" s="0">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="0">
-        <v>0</v>
-      </c>
+      <c r="V4" s="0"/>
+      <c r="W4" s="0"/>
+      <c r="X4" s="0"/>
+      <c r="Y4" s="0"/>
+      <c r="Z4" s="0"/>
+      <c r="AA4" s="0"/>
+      <c r="AB4" s="0"/>
+      <c r="AC4" s="0"/>
+      <c r="AD4" s="0"/>
+      <c r="AE4" s="0"/>
+      <c r="AF4" s="0"/>
+      <c r="AG4" s="0"/>
+      <c r="AH4" s="0"/>
+      <c r="AI4" s="0"/>
+      <c r="AJ4" s="0"/>
+      <c r="AK4" s="0"/>
       <c r="AL4" s="0"/>
-      <c r="AM4" s="0">
-        <v>0.17599999999999999</v>
-      </c>
-      <c r="AN4" s="0">
-        <v>0.69399999999999995</v>
-      </c>
-      <c r="AO4" s="0">
-        <v>-5.6802541313871178</v>
-      </c>
-      <c r="AP4" s="0">
-        <v>0.41999999999999998</v>
-      </c>
-      <c r="AQ4" s="0">
-        <v>0</v>
-      </c>
-      <c r="AR4" s="0">
-        <v>-5.3559999999999999</v>
-      </c>
-      <c r="AS4" s="0">
-        <v>0.20599999999999999</v>
-      </c>
-      <c r="AT4" s="0">
-        <v>1.6459999999999999</v>
-      </c>
-      <c r="AU4" s="0">
-        <v>0.001534277463076556</v>
-      </c>
-      <c r="AV4" s="0">
-        <v>0.70799999999999996</v>
-      </c>
-      <c r="AW4" s="0">
-        <v>-0.0065307428117043244</v>
-      </c>
-      <c r="AX4" s="0">
-        <v>0.002</v>
-      </c>
-      <c r="AY4" s="0">
-        <v>0</v>
-      </c>
-      <c r="AZ4" s="0">
-        <v>1</v>
-      </c>
-      <c r="BA4" s="0">
-        <v>0</v>
-      </c>
-      <c r="BB4" s="0">
-        <v>1</v>
-      </c>
+      <c r="AM4" s="0"/>
+      <c r="AN4" s="0"/>
+      <c r="AO4" s="0"/>
+      <c r="AP4" s="0"/>
+      <c r="AQ4" s="0"/>
+      <c r="AR4" s="0"/>
+      <c r="AS4" s="0"/>
+      <c r="AT4" s="0"/>
+      <c r="AU4" s="0"/>
+      <c r="AV4" s="0"/>
+      <c r="AW4" s="0"/>
+      <c r="AX4" s="0"/>
+      <c r="AY4" s="0"/>
+      <c r="AZ4" s="0"/>
+      <c r="BA4" s="0"/>
+      <c r="BB4" s="0"/>
       <c r="BC4" s="0"/>
+      <c r="BD4" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE4" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
@@ -1024,153 +782,63 @@
       <c r="D5" s="0">
         <v>4</v>
       </c>
-      <c r="E5" s="0">
-        <v>0.26200000000000001</v>
-      </c>
-      <c r="F5" s="0">
-        <v>0.874</v>
-      </c>
-      <c r="G5" s="0">
-        <v>-0.3244131949310578</v>
-      </c>
-      <c r="H5" s="0">
-        <v>0.55400000000000005</v>
-      </c>
-      <c r="I5" s="0">
-        <v>0</v>
-      </c>
-      <c r="J5" s="0">
-        <v>-4.8319999999999999</v>
-      </c>
-      <c r="K5" s="0">
-        <v>0.52000000000000002</v>
-      </c>
-      <c r="L5" s="0">
-        <v>1.268</v>
-      </c>
-      <c r="M5" s="0">
-        <v>-0.0018504791757648525</v>
-      </c>
-      <c r="N5" s="0">
-        <v>0.83999999999999997</v>
-      </c>
-      <c r="O5" s="0">
-        <v>-0.043500961175947567</v>
-      </c>
-      <c r="P5" s="0">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="0">
-        <v>0</v>
-      </c>
-      <c r="R5" s="0">
-        <v>1</v>
-      </c>
-      <c r="S5" s="0">
-        <v>0</v>
-      </c>
-      <c r="T5" s="0">
-        <v>1</v>
-      </c>
+      <c r="E5" s="0"/>
+      <c r="F5" s="0"/>
+      <c r="G5" s="0"/>
+      <c r="H5" s="0"/>
+      <c r="I5" s="0"/>
+      <c r="J5" s="0"/>
+      <c r="K5" s="0"/>
+      <c r="L5" s="0"/>
+      <c r="M5" s="0"/>
+      <c r="N5" s="0"/>
+      <c r="O5" s="0"/>
+      <c r="P5" s="0"/>
+      <c r="Q5" s="0"/>
+      <c r="R5" s="0"/>
+      <c r="S5" s="0"/>
+      <c r="T5" s="0"/>
       <c r="U5" s="0"/>
-      <c r="V5" s="0">
-        <v>0.25</v>
-      </c>
-      <c r="W5" s="0">
-        <v>0.98199999999999998</v>
-      </c>
-      <c r="X5" s="0">
-        <v>-0.14713923991421751</v>
-      </c>
-      <c r="Y5" s="0">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="Z5" s="0">
-        <v>-1.0364205392821013</v>
-      </c>
-      <c r="AA5" s="0">
-        <v>-5.4950000000000001</v>
-      </c>
-      <c r="AB5" s="0">
-        <v>0.184</v>
-      </c>
-      <c r="AC5" s="0">
-        <v>1.1080000000000001</v>
-      </c>
-      <c r="AD5" s="0">
-        <v>-0.0053996728666249882</v>
-      </c>
-      <c r="AE5" s="0">
-        <v>0.63800000000000001</v>
-      </c>
-      <c r="AF5" s="0">
-        <v>-0.017705303864178089</v>
-      </c>
-      <c r="AG5" s="0">
-        <v>0.002</v>
-      </c>
-      <c r="AH5" s="0">
-        <v>0</v>
-      </c>
-      <c r="AI5" s="0">
-        <v>1</v>
-      </c>
-      <c r="AJ5" s="0">
-        <v>1</v>
-      </c>
-      <c r="AK5" s="0">
-        <v>1</v>
-      </c>
+      <c r="V5" s="0"/>
+      <c r="W5" s="0"/>
+      <c r="X5" s="0"/>
+      <c r="Y5" s="0"/>
+      <c r="Z5" s="0"/>
+      <c r="AA5" s="0"/>
+      <c r="AB5" s="0"/>
+      <c r="AC5" s="0"/>
+      <c r="AD5" s="0"/>
+      <c r="AE5" s="0"/>
+      <c r="AF5" s="0"/>
+      <c r="AG5" s="0"/>
+      <c r="AH5" s="0"/>
+      <c r="AI5" s="0"/>
+      <c r="AJ5" s="0"/>
+      <c r="AK5" s="0"/>
       <c r="AL5" s="0"/>
-      <c r="AM5" s="0">
-        <v>0.156</v>
-      </c>
-      <c r="AN5" s="0">
-        <v>1.8</v>
-      </c>
-      <c r="AO5" s="0">
-        <v>-5.3624688521198305</v>
-      </c>
-      <c r="AP5" s="0">
-        <v>0.438</v>
-      </c>
-      <c r="AQ5" s="0">
-        <v>-0.31832172912427126</v>
-      </c>
-      <c r="AR5" s="0">
-        <v>-5.4950000000000001</v>
-      </c>
-      <c r="AS5" s="0">
-        <v>0.318</v>
-      </c>
-      <c r="AT5" s="0">
-        <v>1.6719999999999999</v>
-      </c>
-      <c r="AU5" s="0">
-        <v>0.00024786933258871</v>
-      </c>
-      <c r="AV5" s="0">
-        <v>0.96399999999999997</v>
-      </c>
-      <c r="AW5" s="0">
-        <v>0</v>
-      </c>
-      <c r="AX5" s="0">
-        <v>0.002</v>
-      </c>
-      <c r="AY5" s="0">
-        <v>0</v>
-      </c>
-      <c r="AZ5" s="0">
-        <v>1</v>
-      </c>
-      <c r="BA5" s="0">
-        <v>0</v>
-      </c>
-      <c r="BB5" s="0">
-        <v>1</v>
-      </c>
+      <c r="AM5" s="0"/>
+      <c r="AN5" s="0"/>
+      <c r="AO5" s="0"/>
+      <c r="AP5" s="0"/>
+      <c r="AQ5" s="0"/>
+      <c r="AR5" s="0"/>
+      <c r="AS5" s="0"/>
+      <c r="AT5" s="0"/>
+      <c r="AU5" s="0"/>
+      <c r="AV5" s="0"/>
+      <c r="AW5" s="0"/>
+      <c r="AX5" s="0"/>
+      <c r="AY5" s="0"/>
+      <c r="AZ5" s="0"/>
+      <c r="BA5" s="0"/>
+      <c r="BB5" s="0"/>
       <c r="BC5" s="0"/>
+      <c r="BD5" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE5" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
@@ -1185,153 +853,63 @@
       <c r="D6" s="0">
         <v>5</v>
       </c>
-      <c r="E6" s="0">
-        <v>0.16800000000000001</v>
-      </c>
-      <c r="F6" s="0">
-        <v>1.3420000000000001</v>
-      </c>
-      <c r="G6" s="0">
-        <v>-4.5537191053631894</v>
-      </c>
-      <c r="H6" s="0">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="I6" s="0">
-        <v>0</v>
-      </c>
-      <c r="J6" s="0">
-        <v>-4.516</v>
-      </c>
-      <c r="K6" s="0">
-        <v>0.17000000000000001</v>
-      </c>
-      <c r="L6" s="0">
-        <v>0.78800000000000003</v>
-      </c>
-      <c r="M6" s="0">
-        <v>-0.0016784298500860779</v>
-      </c>
-      <c r="N6" s="0">
-        <v>0.45400000000000001</v>
-      </c>
-      <c r="O6" s="0">
-        <v>0</v>
-      </c>
-      <c r="P6" s="0">
-        <v>-0.0089999999999999993</v>
-      </c>
-      <c r="Q6" s="0">
-        <v>-0</v>
-      </c>
-      <c r="R6" s="0">
-        <v>1</v>
-      </c>
-      <c r="S6" s="0">
-        <v>0</v>
-      </c>
-      <c r="T6" s="0">
-        <v>1</v>
-      </c>
+      <c r="E6" s="0"/>
+      <c r="F6" s="0"/>
+      <c r="G6" s="0"/>
+      <c r="H6" s="0"/>
+      <c r="I6" s="0"/>
+      <c r="J6" s="0"/>
+      <c r="K6" s="0"/>
+      <c r="L6" s="0"/>
+      <c r="M6" s="0"/>
+      <c r="N6" s="0"/>
+      <c r="O6" s="0"/>
+      <c r="P6" s="0"/>
+      <c r="Q6" s="0"/>
+      <c r="R6" s="0"/>
+      <c r="S6" s="0"/>
+      <c r="T6" s="0"/>
       <c r="U6" s="0"/>
-      <c r="V6" s="0">
-        <v>0.14199999999999999</v>
-      </c>
-      <c r="W6" s="0">
-        <v>0.76400000000000001</v>
-      </c>
-      <c r="X6" s="0">
-        <v>-5.2396888289520183</v>
-      </c>
-      <c r="Y6" s="0">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="Z6" s="0">
-        <v>-0.2063134770509123</v>
-      </c>
-      <c r="AA6" s="0">
-        <v>-5.1589999999999998</v>
-      </c>
-      <c r="AB6" s="0">
-        <v>0.158</v>
-      </c>
-      <c r="AC6" s="0">
-        <v>1.454</v>
-      </c>
-      <c r="AD6" s="0">
-        <v>-0.010853021726775899</v>
-      </c>
-      <c r="AE6" s="0">
-        <v>0.84799999999999998</v>
-      </c>
-      <c r="AF6" s="0">
-        <v>-0.0060666516752019665</v>
-      </c>
-      <c r="AG6" s="0">
-        <v>-0.0089999999999999993</v>
-      </c>
-      <c r="AH6" s="0">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="0">
-        <v>1</v>
-      </c>
-      <c r="AJ6" s="0">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="0">
-        <v>1</v>
-      </c>
+      <c r="V6" s="0"/>
+      <c r="W6" s="0"/>
+      <c r="X6" s="0"/>
+      <c r="Y6" s="0"/>
+      <c r="Z6" s="0"/>
+      <c r="AA6" s="0"/>
+      <c r="AB6" s="0"/>
+      <c r="AC6" s="0"/>
+      <c r="AD6" s="0"/>
+      <c r="AE6" s="0"/>
+      <c r="AF6" s="0"/>
+      <c r="AG6" s="0"/>
+      <c r="AH6" s="0"/>
+      <c r="AI6" s="0"/>
+      <c r="AJ6" s="0"/>
+      <c r="AK6" s="0"/>
       <c r="AL6" s="0"/>
-      <c r="AM6" s="0">
-        <v>0.14199999999999999</v>
-      </c>
-      <c r="AN6" s="0">
-        <v>1.1060000000000001</v>
-      </c>
-      <c r="AO6" s="0">
-        <v>-5.2988550129058112</v>
-      </c>
-      <c r="AP6" s="0">
-        <v>0.59199999999999997</v>
-      </c>
-      <c r="AQ6" s="0">
-        <v>-0.85444961270964015</v>
-      </c>
-      <c r="AR6" s="0">
-        <v>-5.1589999999999998</v>
-      </c>
-      <c r="AS6" s="0">
-        <v>0.29199999999999998</v>
-      </c>
-      <c r="AT6" s="0">
-        <v>0.92600000000000005</v>
-      </c>
-      <c r="AU6" s="0">
-        <v>-0.0060702070949607972</v>
-      </c>
-      <c r="AV6" s="0">
-        <v>0.60399999999999998</v>
-      </c>
-      <c r="AW6" s="0">
-        <v>-0.0047103794563696467</v>
-      </c>
-      <c r="AX6" s="0">
-        <v>-0.0089999999999999993</v>
-      </c>
-      <c r="AY6" s="0">
-        <v>0</v>
-      </c>
-      <c r="AZ6" s="0">
-        <v>1</v>
-      </c>
-      <c r="BA6" s="0">
-        <v>1</v>
-      </c>
-      <c r="BB6" s="0">
-        <v>0</v>
-      </c>
+      <c r="AM6" s="0"/>
+      <c r="AN6" s="0"/>
+      <c r="AO6" s="0"/>
+      <c r="AP6" s="0"/>
+      <c r="AQ6" s="0"/>
+      <c r="AR6" s="0"/>
+      <c r="AS6" s="0"/>
+      <c r="AT6" s="0"/>
+      <c r="AU6" s="0"/>
+      <c r="AV6" s="0"/>
+      <c r="AW6" s="0"/>
+      <c r="AX6" s="0"/>
+      <c r="AY6" s="0"/>
+      <c r="AZ6" s="0"/>
+      <c r="BA6" s="0"/>
+      <c r="BB6" s="0"/>
       <c r="BC6" s="0"/>
+      <c r="BD6" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE6" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
@@ -1346,153 +924,63 @@
       <c r="D7" s="0">
         <v>6</v>
       </c>
-      <c r="E7" s="0">
-        <v>0.19</v>
-      </c>
-      <c r="F7" s="0">
-        <v>1</v>
-      </c>
-      <c r="G7" s="0">
-        <v>-4.5644640702208381</v>
-      </c>
-      <c r="H7" s="0">
-        <v>0.52400000000000002</v>
-      </c>
-      <c r="I7" s="0">
-        <v>-0.82894630174301653</v>
-      </c>
-      <c r="J7" s="0">
-        <v>-4.5030000000000001</v>
-      </c>
-      <c r="K7" s="0">
-        <v>0.47599999999999998</v>
-      </c>
-      <c r="L7" s="0">
-        <v>1.466</v>
-      </c>
-      <c r="M7" s="0">
-        <v>-0.0013273854740360714</v>
-      </c>
-      <c r="N7" s="0">
-        <v>0.94799999999999995</v>
-      </c>
-      <c r="O7" s="0">
-        <v>0.037921460631983303</v>
-      </c>
-      <c r="P7" s="0">
-        <v>0.001</v>
-      </c>
-      <c r="Q7" s="0">
-        <v>-0</v>
-      </c>
-      <c r="R7" s="0">
-        <v>1</v>
-      </c>
-      <c r="S7" s="0">
-        <v>1</v>
-      </c>
-      <c r="T7" s="0">
-        <v>0</v>
-      </c>
+      <c r="E7" s="0"/>
+      <c r="F7" s="0"/>
+      <c r="G7" s="0"/>
+      <c r="H7" s="0"/>
+      <c r="I7" s="0"/>
+      <c r="J7" s="0"/>
+      <c r="K7" s="0"/>
+      <c r="L7" s="0"/>
+      <c r="M7" s="0"/>
+      <c r="N7" s="0"/>
+      <c r="O7" s="0"/>
+      <c r="P7" s="0"/>
+      <c r="Q7" s="0"/>
+      <c r="R7" s="0"/>
+      <c r="S7" s="0"/>
+      <c r="T7" s="0"/>
       <c r="U7" s="0"/>
-      <c r="V7" s="0">
-        <v>0.17199999999999999</v>
-      </c>
-      <c r="W7" s="0">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="X7" s="0">
-        <v>-5.0603146432699546</v>
-      </c>
-      <c r="Y7" s="0">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="Z7" s="0">
-        <v>-0.34228539111991196</v>
-      </c>
-      <c r="AA7" s="0">
-        <v>-4.7779999999999996</v>
-      </c>
-      <c r="AB7" s="0">
-        <v>0.224</v>
-      </c>
-      <c r="AC7" s="0">
-        <v>1.1479999999999999</v>
-      </c>
-      <c r="AD7" s="0">
-        <v>-0.0022673074668481813</v>
-      </c>
-      <c r="AE7" s="0">
-        <v>0.63400000000000001</v>
-      </c>
-      <c r="AF7" s="0">
-        <v>-0.0027853519582268262</v>
-      </c>
-      <c r="AG7" s="0">
-        <v>0.0030000000000000001</v>
-      </c>
-      <c r="AH7" s="0">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="0">
-        <v>1</v>
-      </c>
-      <c r="AJ7" s="0">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="0">
-        <v>0</v>
-      </c>
+      <c r="V7" s="0"/>
+      <c r="W7" s="0"/>
+      <c r="X7" s="0"/>
+      <c r="Y7" s="0"/>
+      <c r="Z7" s="0"/>
+      <c r="AA7" s="0"/>
+      <c r="AB7" s="0"/>
+      <c r="AC7" s="0"/>
+      <c r="AD7" s="0"/>
+      <c r="AE7" s="0"/>
+      <c r="AF7" s="0"/>
+      <c r="AG7" s="0"/>
+      <c r="AH7" s="0"/>
+      <c r="AI7" s="0"/>
+      <c r="AJ7" s="0"/>
+      <c r="AK7" s="0"/>
       <c r="AL7" s="0"/>
-      <c r="AM7" s="0">
-        <v>0.254</v>
-      </c>
-      <c r="AN7" s="0">
-        <v>0.82399999999999995</v>
-      </c>
-      <c r="AO7" s="0">
-        <v>-0.09876199317181289</v>
-      </c>
-      <c r="AP7" s="0">
-        <v>0.502</v>
-      </c>
-      <c r="AQ7" s="0">
-        <v>0</v>
-      </c>
-      <c r="AR7" s="0">
-        <v>-4.7779999999999996</v>
-      </c>
-      <c r="AS7" s="0">
-        <v>0.53600000000000003</v>
-      </c>
-      <c r="AT7" s="0">
-        <v>1.3720000000000001</v>
-      </c>
-      <c r="AU7" s="0">
-        <v>-0.00076094818896842219</v>
-      </c>
-      <c r="AV7" s="0">
-        <v>0.83999999999999997</v>
-      </c>
-      <c r="AW7" s="0">
-        <v>0.0055063854121677408</v>
-      </c>
-      <c r="AX7" s="0">
-        <v>0.0030000000000000001</v>
-      </c>
-      <c r="AY7" s="0">
-        <v>0</v>
-      </c>
-      <c r="AZ7" s="0">
-        <v>1</v>
-      </c>
-      <c r="BA7" s="0">
-        <v>0</v>
-      </c>
-      <c r="BB7" s="0">
-        <v>1</v>
-      </c>
+      <c r="AM7" s="0"/>
+      <c r="AN7" s="0"/>
+      <c r="AO7" s="0"/>
+      <c r="AP7" s="0"/>
+      <c r="AQ7" s="0"/>
+      <c r="AR7" s="0"/>
+      <c r="AS7" s="0"/>
+      <c r="AT7" s="0"/>
+      <c r="AU7" s="0"/>
+      <c r="AV7" s="0"/>
+      <c r="AW7" s="0"/>
+      <c r="AX7" s="0"/>
+      <c r="AY7" s="0"/>
+      <c r="AZ7" s="0"/>
+      <c r="BA7" s="0"/>
+      <c r="BB7" s="0"/>
       <c r="BC7" s="0"/>
+      <c r="BD7" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE7" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
@@ -1507,153 +995,63 @@
       <c r="D8" s="0">
         <v>7</v>
       </c>
-      <c r="E8" s="0">
-        <v>0.25</v>
-      </c>
-      <c r="F8" s="0">
-        <v>0.874</v>
-      </c>
-      <c r="G8" s="0">
-        <v>-0.28342736556519998</v>
-      </c>
-      <c r="H8" s="0">
-        <v>0.498</v>
-      </c>
-      <c r="I8" s="0">
-        <v>0</v>
-      </c>
-      <c r="J8" s="0">
-        <v>-4.6600000000000001</v>
-      </c>
-      <c r="K8" s="0">
-        <v>0.20200000000000001</v>
-      </c>
-      <c r="L8" s="0">
-        <v>0.86599999999999999</v>
-      </c>
-      <c r="M8" s="0">
-        <v>-0.00601732422914859</v>
-      </c>
-      <c r="N8" s="0">
-        <v>0.49399999999999999</v>
-      </c>
-      <c r="O8" s="0">
-        <v>-0.0076973162273933152</v>
-      </c>
-      <c r="P8" s="0">
-        <v>0.001</v>
-      </c>
-      <c r="Q8" s="0">
-        <v>0</v>
-      </c>
-      <c r="R8" s="0">
-        <v>1</v>
-      </c>
-      <c r="S8" s="0">
-        <v>1</v>
-      </c>
-      <c r="T8" s="0">
-        <v>1</v>
-      </c>
+      <c r="E8" s="0"/>
+      <c r="F8" s="0"/>
+      <c r="G8" s="0"/>
+      <c r="H8" s="0"/>
+      <c r="I8" s="0"/>
+      <c r="J8" s="0"/>
+      <c r="K8" s="0"/>
+      <c r="L8" s="0"/>
+      <c r="M8" s="0"/>
+      <c r="N8" s="0"/>
+      <c r="O8" s="0"/>
+      <c r="P8" s="0"/>
+      <c r="Q8" s="0"/>
+      <c r="R8" s="0"/>
+      <c r="S8" s="0"/>
+      <c r="T8" s="0"/>
       <c r="U8" s="0"/>
-      <c r="V8" s="0">
-        <v>0.23599999999999999</v>
-      </c>
-      <c r="W8" s="0">
-        <v>1.016</v>
-      </c>
-      <c r="X8" s="0">
-        <v>-0.046679187045682191</v>
-      </c>
-      <c r="Y8" s="0">
-        <v>0.60399999999999998</v>
-      </c>
-      <c r="Z8" s="0">
-        <v>-0.48816054406231046</v>
-      </c>
-      <c r="AA8" s="0">
-        <v>-4.8949999999999996</v>
-      </c>
-      <c r="AB8" s="0">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="AC8" s="0">
-        <v>1.4279999999999999</v>
-      </c>
-      <c r="AD8" s="0">
-        <v>-0.0058095672774958994</v>
-      </c>
-      <c r="AE8" s="0">
-        <v>1.004</v>
-      </c>
-      <c r="AF8" s="0">
-        <v>-0.010297500421176976</v>
-      </c>
-      <c r="AG8" s="0">
-        <v>0.001</v>
-      </c>
-      <c r="AH8" s="0">
-        <v>-0</v>
-      </c>
-      <c r="AI8" s="0">
-        <v>1</v>
-      </c>
-      <c r="AJ8" s="0">
-        <v>0</v>
-      </c>
-      <c r="AK8" s="0">
-        <v>0</v>
-      </c>
+      <c r="V8" s="0"/>
+      <c r="W8" s="0"/>
+      <c r="X8" s="0"/>
+      <c r="Y8" s="0"/>
+      <c r="Z8" s="0"/>
+      <c r="AA8" s="0"/>
+      <c r="AB8" s="0"/>
+      <c r="AC8" s="0"/>
+      <c r="AD8" s="0"/>
+      <c r="AE8" s="0"/>
+      <c r="AF8" s="0"/>
+      <c r="AG8" s="0"/>
+      <c r="AH8" s="0"/>
+      <c r="AI8" s="0"/>
+      <c r="AJ8" s="0"/>
+      <c r="AK8" s="0"/>
       <c r="AL8" s="0"/>
-      <c r="AM8" s="0">
-        <v>0.152</v>
-      </c>
-      <c r="AN8" s="0">
-        <v>0.81999999999999995</v>
-      </c>
-      <c r="AO8" s="0">
-        <v>-5.0214689757203583</v>
-      </c>
-      <c r="AP8" s="0">
-        <v>0.29999999999999999</v>
-      </c>
-      <c r="AQ8" s="0">
-        <v>1.0994563846860039</v>
-      </c>
-      <c r="AR8" s="0">
-        <v>-4.8949999999999996</v>
-      </c>
-      <c r="AS8" s="0">
-        <v>0.35999999999999999</v>
-      </c>
-      <c r="AT8" s="0">
-        <v>1.0640000000000001</v>
-      </c>
-      <c r="AU8" s="0">
-        <v>-0.0079010338448687011</v>
-      </c>
-      <c r="AV8" s="0">
-        <v>0.66000000000000003</v>
-      </c>
-      <c r="AW8" s="0">
-        <v>-0.022708069728283774</v>
-      </c>
-      <c r="AX8" s="0">
-        <v>0.001</v>
-      </c>
-      <c r="AY8" s="0">
-        <v>-0</v>
-      </c>
-      <c r="AZ8" s="0">
-        <v>1</v>
-      </c>
-      <c r="BA8" s="0">
-        <v>0</v>
-      </c>
-      <c r="BB8" s="0">
-        <v>1</v>
-      </c>
+      <c r="AM8" s="0"/>
+      <c r="AN8" s="0"/>
+      <c r="AO8" s="0"/>
+      <c r="AP8" s="0"/>
+      <c r="AQ8" s="0"/>
+      <c r="AR8" s="0"/>
+      <c r="AS8" s="0"/>
+      <c r="AT8" s="0"/>
+      <c r="AU8" s="0"/>
+      <c r="AV8" s="0"/>
+      <c r="AW8" s="0"/>
+      <c r="AX8" s="0"/>
+      <c r="AY8" s="0"/>
+      <c r="AZ8" s="0"/>
+      <c r="BA8" s="0"/>
+      <c r="BB8" s="0"/>
       <c r="BC8" s="0"/>
+      <c r="BD8" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE8" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
@@ -1668,153 +1066,63 @@
       <c r="D9" s="0">
         <v>8</v>
       </c>
-      <c r="E9" s="0">
-        <v>0.23599999999999999</v>
-      </c>
-      <c r="F9" s="0">
-        <v>1.0580000000000001</v>
-      </c>
-      <c r="G9" s="0">
-        <v>-0.66271272981153606</v>
-      </c>
-      <c r="H9" s="0">
-        <v>0.46800000000000003</v>
-      </c>
-      <c r="I9" s="0">
-        <v>0</v>
-      </c>
-      <c r="J9" s="0">
-        <v>-4.444</v>
-      </c>
-      <c r="K9" s="0">
-        <v>0.254</v>
-      </c>
-      <c r="L9" s="0">
-        <v>1.208</v>
-      </c>
-      <c r="M9" s="0">
-        <v>-0.0054559168621585458</v>
-      </c>
-      <c r="N9" s="0">
-        <v>0.67400000000000004</v>
-      </c>
-      <c r="O9" s="0">
-        <v>-0.013508181473197763</v>
-      </c>
-      <c r="P9" s="0">
-        <v>0.001</v>
-      </c>
-      <c r="Q9" s="0">
-        <v>-0</v>
-      </c>
-      <c r="R9" s="0">
-        <v>1</v>
-      </c>
-      <c r="S9" s="0">
-        <v>0</v>
-      </c>
-      <c r="T9" s="0">
-        <v>1</v>
-      </c>
+      <c r="E9" s="0"/>
+      <c r="F9" s="0"/>
+      <c r="G9" s="0"/>
+      <c r="H9" s="0"/>
+      <c r="I9" s="0"/>
+      <c r="J9" s="0"/>
+      <c r="K9" s="0"/>
+      <c r="L9" s="0"/>
+      <c r="M9" s="0"/>
+      <c r="N9" s="0"/>
+      <c r="O9" s="0"/>
+      <c r="P9" s="0"/>
+      <c r="Q9" s="0"/>
+      <c r="R9" s="0"/>
+      <c r="S9" s="0"/>
+      <c r="T9" s="0"/>
       <c r="U9" s="0"/>
-      <c r="V9" s="0">
-        <v>0.14599999999999999</v>
-      </c>
-      <c r="W9" s="0">
-        <v>1.024</v>
-      </c>
-      <c r="X9" s="0">
-        <v>-5.1180441672310639</v>
-      </c>
-      <c r="Y9" s="0">
-        <v>0.54000000000000004</v>
-      </c>
-      <c r="Z9" s="0">
-        <v>-0.52318153355779273</v>
-      </c>
-      <c r="AA9" s="0">
-        <v>-5.0119999999999996</v>
-      </c>
-      <c r="AB9" s="0">
-        <v>0.32200000000000001</v>
-      </c>
-      <c r="AC9" s="0">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="AD9" s="0">
-        <v>-0.0037532233435799288</v>
-      </c>
-      <c r="AE9" s="0">
-        <v>0.72399999999999998</v>
-      </c>
-      <c r="AF9" s="0">
-        <v>-0.0045151090608736878</v>
-      </c>
-      <c r="AG9" s="0">
-        <v>-0.001</v>
-      </c>
-      <c r="AH9" s="0">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="0">
-        <v>0</v>
-      </c>
-      <c r="AJ9" s="0">
-        <v>1</v>
-      </c>
-      <c r="AK9" s="0">
-        <v>1</v>
-      </c>
+      <c r="V9" s="0"/>
+      <c r="W9" s="0"/>
+      <c r="X9" s="0"/>
+      <c r="Y9" s="0"/>
+      <c r="Z9" s="0"/>
+      <c r="AA9" s="0"/>
+      <c r="AB9" s="0"/>
+      <c r="AC9" s="0"/>
+      <c r="AD9" s="0"/>
+      <c r="AE9" s="0"/>
+      <c r="AF9" s="0"/>
+      <c r="AG9" s="0"/>
+      <c r="AH9" s="0"/>
+      <c r="AI9" s="0"/>
+      <c r="AJ9" s="0"/>
+      <c r="AK9" s="0"/>
       <c r="AL9" s="0"/>
-      <c r="AM9" s="0">
-        <v>0.23999999999999999</v>
-      </c>
-      <c r="AN9" s="0">
-        <v>1.482</v>
-      </c>
-      <c r="AO9" s="0">
-        <v>-0.30697911306072179</v>
-      </c>
-      <c r="AP9" s="0">
-        <v>0.74199999999999999</v>
-      </c>
-      <c r="AQ9" s="0">
-        <v>0</v>
-      </c>
-      <c r="AR9" s="0">
-        <v>-5.0119999999999996</v>
-      </c>
-      <c r="AS9" s="0">
-        <v>0.35999999999999999</v>
-      </c>
-      <c r="AT9" s="0">
-        <v>1.016</v>
-      </c>
-      <c r="AU9" s="0">
-        <v>-0.0058833758920517351</v>
-      </c>
-      <c r="AV9" s="0">
-        <v>0.64800000000000002</v>
-      </c>
-      <c r="AW9" s="0">
-        <v>-0.014560040623893839</v>
-      </c>
-      <c r="AX9" s="0">
-        <v>-0.001</v>
-      </c>
-      <c r="AY9" s="0">
-        <v>0</v>
-      </c>
-      <c r="AZ9" s="0">
-        <v>1</v>
-      </c>
-      <c r="BA9" s="0">
-        <v>0</v>
-      </c>
-      <c r="BB9" s="0">
-        <v>0</v>
-      </c>
+      <c r="AM9" s="0"/>
+      <c r="AN9" s="0"/>
+      <c r="AO9" s="0"/>
+      <c r="AP9" s="0"/>
+      <c r="AQ9" s="0"/>
+      <c r="AR9" s="0"/>
+      <c r="AS9" s="0"/>
+      <c r="AT9" s="0"/>
+      <c r="AU9" s="0"/>
+      <c r="AV9" s="0"/>
+      <c r="AW9" s="0"/>
+      <c r="AX9" s="0"/>
+      <c r="AY9" s="0"/>
+      <c r="AZ9" s="0"/>
+      <c r="BA9" s="0"/>
+      <c r="BB9" s="0"/>
       <c r="BC9" s="0"/>
+      <c r="BD9" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE9" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
@@ -1829,153 +1137,63 @@
       <c r="D10" s="0">
         <v>9</v>
       </c>
-      <c r="E10" s="0">
-        <v>0.246</v>
-      </c>
-      <c r="F10" s="0">
-        <v>0.87</v>
-      </c>
-      <c r="G10" s="0">
-        <v>-0.53548380336322676</v>
-      </c>
-      <c r="H10" s="0">
-        <v>0.51000000000000001</v>
-      </c>
-      <c r="I10" s="0">
-        <v>-0.28490475661735459</v>
-      </c>
-      <c r="J10" s="0">
-        <v>-4.6120000000000001</v>
-      </c>
-      <c r="K10" s="0">
-        <v>0.154</v>
-      </c>
-      <c r="L10" s="0">
-        <v>1.202</v>
-      </c>
-      <c r="M10" s="0">
-        <v>-0.0055271444340315185</v>
-      </c>
-      <c r="N10" s="0">
-        <v>0.68000000000000005</v>
-      </c>
-      <c r="O10" s="0">
-        <v>-0.0067263302651987371</v>
-      </c>
-      <c r="P10" s="0">
-        <v>-0.0089999999999999993</v>
-      </c>
-      <c r="Q10" s="0">
-        <v>-0</v>
-      </c>
-      <c r="R10" s="0">
-        <v>1</v>
-      </c>
-      <c r="S10" s="0">
-        <v>0</v>
-      </c>
-      <c r="T10" s="0">
-        <v>0</v>
-      </c>
+      <c r="E10" s="0"/>
+      <c r="F10" s="0"/>
+      <c r="G10" s="0"/>
+      <c r="H10" s="0"/>
+      <c r="I10" s="0"/>
+      <c r="J10" s="0"/>
+      <c r="K10" s="0"/>
+      <c r="L10" s="0"/>
+      <c r="M10" s="0"/>
+      <c r="N10" s="0"/>
+      <c r="O10" s="0"/>
+      <c r="P10" s="0"/>
+      <c r="Q10" s="0"/>
+      <c r="R10" s="0"/>
+      <c r="S10" s="0"/>
+      <c r="T10" s="0"/>
       <c r="U10" s="0"/>
-      <c r="V10" s="0">
-        <v>0.16800000000000001</v>
-      </c>
-      <c r="W10" s="0">
-        <v>0.73799999999999999</v>
-      </c>
-      <c r="X10" s="0">
-        <v>-5.0162520414430443</v>
-      </c>
-      <c r="Y10" s="0">
-        <v>0.40000000000000002</v>
-      </c>
-      <c r="Z10" s="0">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="0">
-        <v>-5.0860000000000003</v>
-      </c>
-      <c r="AB10" s="0">
-        <v>0.17599999999999999</v>
-      </c>
-      <c r="AC10" s="0">
-        <v>0.80200000000000005</v>
-      </c>
-      <c r="AD10" s="0">
-        <v>-0.0020812305893942199</v>
-      </c>
-      <c r="AE10" s="0">
-        <v>0.50600000000000001</v>
-      </c>
-      <c r="AF10" s="0">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="0">
-        <v>-0.0089999999999999993</v>
-      </c>
-      <c r="AH10" s="0">
-        <v>-0</v>
-      </c>
-      <c r="AI10" s="0">
-        <v>1</v>
-      </c>
-      <c r="AJ10" s="0">
-        <v>1</v>
-      </c>
-      <c r="AK10" s="0">
-        <v>0</v>
-      </c>
+      <c r="V10" s="0"/>
+      <c r="W10" s="0"/>
+      <c r="X10" s="0"/>
+      <c r="Y10" s="0"/>
+      <c r="Z10" s="0"/>
+      <c r="AA10" s="0"/>
+      <c r="AB10" s="0"/>
+      <c r="AC10" s="0"/>
+      <c r="AD10" s="0"/>
+      <c r="AE10" s="0"/>
+      <c r="AF10" s="0"/>
+      <c r="AG10" s="0"/>
+      <c r="AH10" s="0"/>
+      <c r="AI10" s="0"/>
+      <c r="AJ10" s="0"/>
+      <c r="AK10" s="0"/>
       <c r="AL10" s="0"/>
-      <c r="AM10" s="0">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="AN10" s="0">
-        <v>0.98599999999999999</v>
-      </c>
-      <c r="AO10" s="0">
-        <v>-5.0705318635200936</v>
-      </c>
-      <c r="AP10" s="0">
-        <v>0.51600000000000001</v>
-      </c>
-      <c r="AQ10" s="0">
-        <v>-0.2527883784337881</v>
-      </c>
-      <c r="AR10" s="0">
-        <v>-5.0860000000000003</v>
-      </c>
-      <c r="AS10" s="0">
-        <v>0.14999999999999999</v>
-      </c>
-      <c r="AT10" s="0">
-        <v>0.88</v>
-      </c>
-      <c r="AU10" s="0">
-        <v>-0.0035592831494459616</v>
-      </c>
-      <c r="AV10" s="0">
-        <v>0.46999999999999997</v>
-      </c>
-      <c r="AW10" s="0">
-        <v>0.004663328993086753</v>
-      </c>
-      <c r="AX10" s="0">
-        <v>-0.0089999999999999993</v>
-      </c>
-      <c r="AY10" s="0">
-        <v>-0</v>
-      </c>
-      <c r="AZ10" s="0">
-        <v>1</v>
-      </c>
-      <c r="BA10" s="0">
-        <v>0</v>
-      </c>
-      <c r="BB10" s="0">
-        <v>1</v>
-      </c>
+      <c r="AM10" s="0"/>
+      <c r="AN10" s="0"/>
+      <c r="AO10" s="0"/>
+      <c r="AP10" s="0"/>
+      <c r="AQ10" s="0"/>
+      <c r="AR10" s="0"/>
+      <c r="AS10" s="0"/>
+      <c r="AT10" s="0"/>
+      <c r="AU10" s="0"/>
+      <c r="AV10" s="0"/>
+      <c r="AW10" s="0"/>
+      <c r="AX10" s="0"/>
+      <c r="AY10" s="0"/>
+      <c r="AZ10" s="0"/>
+      <c r="BA10" s="0"/>
+      <c r="BB10" s="0"/>
       <c r="BC10" s="0"/>
+      <c r="BD10" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE10" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
@@ -1990,153 +1208,63 @@
       <c r="D11" s="0">
         <v>10</v>
       </c>
-      <c r="E11" s="0">
-        <v>0.26600000000000001</v>
-      </c>
-      <c r="F11" s="0">
-        <v>0.91000000000000003</v>
-      </c>
-      <c r="G11" s="0">
-        <v>-0.93362586856383256</v>
-      </c>
-      <c r="H11" s="0">
-        <v>0.58399999999999996</v>
-      </c>
-      <c r="I11" s="0">
-        <v>-1.5139376890322964</v>
-      </c>
-      <c r="J11" s="0">
-        <v>-4.8410000000000002</v>
-      </c>
-      <c r="K11" s="0">
-        <v>0.23599999999999999</v>
-      </c>
-      <c r="L11" s="0">
-        <v>1.044</v>
-      </c>
-      <c r="M11" s="0">
-        <v>-0.01048669456413109</v>
-      </c>
-      <c r="N11" s="0">
-        <v>0.66200000000000003</v>
-      </c>
-      <c r="O11" s="0">
-        <v>-0.006725864406863756</v>
-      </c>
-      <c r="P11" s="0">
-        <v>-0.0089999999999999993</v>
-      </c>
-      <c r="Q11" s="0">
-        <v>-0</v>
-      </c>
-      <c r="R11" s="0">
-        <v>1</v>
-      </c>
-      <c r="S11" s="0">
-        <v>0</v>
-      </c>
-      <c r="T11" s="0">
-        <v>1</v>
-      </c>
+      <c r="E11" s="0"/>
+      <c r="F11" s="0"/>
+      <c r="G11" s="0"/>
+      <c r="H11" s="0"/>
+      <c r="I11" s="0"/>
+      <c r="J11" s="0"/>
+      <c r="K11" s="0"/>
+      <c r="L11" s="0"/>
+      <c r="M11" s="0"/>
+      <c r="N11" s="0"/>
+      <c r="O11" s="0"/>
+      <c r="P11" s="0"/>
+      <c r="Q11" s="0"/>
+      <c r="R11" s="0"/>
+      <c r="S11" s="0"/>
+      <c r="T11" s="0"/>
       <c r="U11" s="0"/>
-      <c r="V11" s="0">
-        <v>0.16</v>
-      </c>
-      <c r="W11" s="0">
-        <v>0.73399999999999999</v>
-      </c>
-      <c r="X11" s="0">
-        <v>-5.554060037293624</v>
-      </c>
-      <c r="Y11" s="0">
-        <v>0.442</v>
-      </c>
-      <c r="Z11" s="0">
-        <v>-0.54196478016299565</v>
-      </c>
-      <c r="AA11" s="0">
-        <v>-5.3019999999999996</v>
-      </c>
-      <c r="AB11" s="0">
-        <v>0.20999999999999999</v>
-      </c>
-      <c r="AC11" s="0">
-        <v>1.1120000000000001</v>
-      </c>
-      <c r="AD11" s="0">
-        <v>-0.010680961634195409</v>
-      </c>
-      <c r="AE11" s="0">
-        <v>0.72199999999999998</v>
-      </c>
-      <c r="AF11" s="0">
-        <v>-0.011634921219244827</v>
-      </c>
-      <c r="AG11" s="0">
-        <v>-0.01</v>
-      </c>
-      <c r="AH11" s="0">
-        <v>-0</v>
-      </c>
-      <c r="AI11" s="0">
-        <v>0</v>
-      </c>
-      <c r="AJ11" s="0">
-        <v>1</v>
-      </c>
-      <c r="AK11" s="0">
-        <v>1</v>
-      </c>
+      <c r="V11" s="0"/>
+      <c r="W11" s="0"/>
+      <c r="X11" s="0"/>
+      <c r="Y11" s="0"/>
+      <c r="Z11" s="0"/>
+      <c r="AA11" s="0"/>
+      <c r="AB11" s="0"/>
+      <c r="AC11" s="0"/>
+      <c r="AD11" s="0"/>
+      <c r="AE11" s="0"/>
+      <c r="AF11" s="0"/>
+      <c r="AG11" s="0"/>
+      <c r="AH11" s="0"/>
+      <c r="AI11" s="0"/>
+      <c r="AJ11" s="0"/>
+      <c r="AK11" s="0"/>
       <c r="AL11" s="0"/>
-      <c r="AM11" s="0">
-        <v>0.122</v>
-      </c>
-      <c r="AN11" s="0">
-        <v>1.444</v>
-      </c>
-      <c r="AO11" s="0">
-        <v>-5.1474305566394172</v>
-      </c>
-      <c r="AP11" s="0">
-        <v>0.20399999999999999</v>
-      </c>
-      <c r="AQ11" s="0">
-        <v>-122.61128831662616</v>
-      </c>
-      <c r="AR11" s="0">
-        <v>-5.3019999999999996</v>
-      </c>
-      <c r="AS11" s="0">
-        <v>0.27800000000000002</v>
-      </c>
-      <c r="AT11" s="0">
-        <v>1.1240000000000001</v>
-      </c>
-      <c r="AU11" s="0">
-        <v>-0.010903614453028813</v>
-      </c>
-      <c r="AV11" s="0">
-        <v>0.71799999999999997</v>
-      </c>
-      <c r="AW11" s="0">
-        <v>-0.014168851677801584</v>
-      </c>
-      <c r="AX11" s="0">
-        <v>-0.01</v>
-      </c>
-      <c r="AY11" s="0">
-        <v>-0</v>
-      </c>
-      <c r="AZ11" s="0">
-        <v>1</v>
-      </c>
-      <c r="BA11" s="0">
-        <v>0</v>
-      </c>
-      <c r="BB11" s="0">
-        <v>0</v>
-      </c>
+      <c r="AM11" s="0"/>
+      <c r="AN11" s="0"/>
+      <c r="AO11" s="0"/>
+      <c r="AP11" s="0"/>
+      <c r="AQ11" s="0"/>
+      <c r="AR11" s="0"/>
+      <c r="AS11" s="0"/>
+      <c r="AT11" s="0"/>
+      <c r="AU11" s="0"/>
+      <c r="AV11" s="0"/>
+      <c r="AW11" s="0"/>
+      <c r="AX11" s="0"/>
+      <c r="AY11" s="0"/>
+      <c r="AZ11" s="0"/>
+      <c r="BA11" s="0"/>
+      <c r="BB11" s="0"/>
       <c r="BC11" s="0"/>
+      <c r="BD11" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE11" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
@@ -2202,6 +1330,12 @@
       <c r="BA12" s="0"/>
       <c r="BB12" s="0"/>
       <c r="BC12" s="0"/>
+      <c r="BD12" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE12" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
@@ -2267,6 +1401,12 @@
       <c r="BA13" s="0"/>
       <c r="BB13" s="0"/>
       <c r="BC13" s="0"/>
+      <c r="BD13" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE13" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
@@ -2332,6 +1472,12 @@
       <c r="BA14" s="0"/>
       <c r="BB14" s="0"/>
       <c r="BC14" s="0"/>
+      <c r="BD14" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE14" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
@@ -2397,6 +1543,12 @@
       <c r="BA15" s="0"/>
       <c r="BB15" s="0"/>
       <c r="BC15" s="0"/>
+      <c r="BD15" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE15" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
@@ -2462,6 +1614,12 @@
       <c r="BA16" s="0"/>
       <c r="BB16" s="0"/>
       <c r="BC16" s="0"/>
+      <c r="BD16" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE16" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
@@ -2527,6 +1685,12 @@
       <c r="BA17" s="0"/>
       <c r="BB17" s="0"/>
       <c r="BC17" s="0"/>
+      <c r="BD17" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE17" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
@@ -2592,6 +1756,12 @@
       <c r="BA18" s="0"/>
       <c r="BB18" s="0"/>
       <c r="BC18" s="0"/>
+      <c r="BD18" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE18" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
@@ -2657,6 +1827,12 @@
       <c r="BA19" s="0"/>
       <c r="BB19" s="0"/>
       <c r="BC19" s="0"/>
+      <c r="BD19" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE19" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
@@ -2722,6 +1898,12 @@
       <c r="BA20" s="0"/>
       <c r="BB20" s="0"/>
       <c r="BC20" s="0"/>
+      <c r="BD20" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE20" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
@@ -2787,6 +1969,12 @@
       <c r="BA21" s="0"/>
       <c r="BB21" s="0"/>
       <c r="BC21" s="0"/>
+      <c r="BD21" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE21" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
@@ -2852,6 +2040,12 @@
       <c r="BA22" s="0"/>
       <c r="BB22" s="0"/>
       <c r="BC22" s="0"/>
+      <c r="BD22" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE22" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
@@ -2917,6 +2111,12 @@
       <c r="BA23" s="0"/>
       <c r="BB23" s="0"/>
       <c r="BC23" s="0"/>
+      <c r="BD23" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE23" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
@@ -2982,6 +2182,12 @@
       <c r="BA24" s="0"/>
       <c r="BB24" s="0"/>
       <c r="BC24" s="0"/>
+      <c r="BD24" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE24" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
@@ -3047,6 +2253,12 @@
       <c r="BA25" s="0"/>
       <c r="BB25" s="0"/>
       <c r="BC25" s="0"/>
+      <c r="BD25" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE25" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
@@ -3112,6 +2324,12 @@
       <c r="BA26" s="0"/>
       <c r="BB26" s="0"/>
       <c r="BC26" s="0"/>
+      <c r="BD26" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE26" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
@@ -3177,6 +2395,12 @@
       <c r="BA27" s="0"/>
       <c r="BB27" s="0"/>
       <c r="BC27" s="0"/>
+      <c r="BD27" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE27" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
@@ -3242,6 +2466,12 @@
       <c r="BA28" s="0"/>
       <c r="BB28" s="0"/>
       <c r="BC28" s="0"/>
+      <c r="BD28" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE28" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
@@ -3307,6 +2537,12 @@
       <c r="BA29" s="0"/>
       <c r="BB29" s="0"/>
       <c r="BC29" s="0"/>
+      <c r="BD29" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE29" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
@@ -3372,6 +2608,12 @@
       <c r="BA30" s="0"/>
       <c r="BB30" s="0"/>
       <c r="BC30" s="0"/>
+      <c r="BD30" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE30" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
@@ -3437,6 +2679,12 @@
       <c r="BA31" s="0"/>
       <c r="BB31" s="0"/>
       <c r="BC31" s="0"/>
+      <c r="BD31" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE31" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
@@ -3502,6 +2750,12 @@
       <c r="BA32" s="0"/>
       <c r="BB32" s="0"/>
       <c r="BC32" s="0"/>
+      <c r="BD32" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE32" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="s">
@@ -3567,6 +2821,12 @@
       <c r="BA33" s="0"/>
       <c r="BB33" s="0"/>
       <c r="BC33" s="0"/>
+      <c r="BD33" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE33" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
@@ -3632,6 +2892,12 @@
       <c r="BA34" s="0"/>
       <c r="BB34" s="0"/>
       <c r="BC34" s="0"/>
+      <c r="BD34" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE34" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
@@ -3697,6 +2963,12 @@
       <c r="BA35" s="0"/>
       <c r="BB35" s="0"/>
       <c r="BC35" s="0"/>
+      <c r="BD35" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE35" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
@@ -3762,6 +3034,12 @@
       <c r="BA36" s="0"/>
       <c r="BB36" s="0"/>
       <c r="BC36" s="0"/>
+      <c r="BD36" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE36" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
@@ -3827,6 +3105,12 @@
       <c r="BA37" s="0"/>
       <c r="BB37" s="0"/>
       <c r="BC37" s="0"/>
+      <c r="BD37" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE37" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
@@ -3892,6 +3176,12 @@
       <c r="BA38" s="0"/>
       <c r="BB38" s="0"/>
       <c r="BC38" s="0"/>
+      <c r="BD38" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE38" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
@@ -3957,6 +3247,12 @@
       <c r="BA39" s="0"/>
       <c r="BB39" s="0"/>
       <c r="BC39" s="0"/>
+      <c r="BD39" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE39" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
@@ -4022,6 +3318,12 @@
       <c r="BA40" s="0"/>
       <c r="BB40" s="0"/>
       <c r="BC40" s="0"/>
+      <c r="BD40" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE40" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
@@ -4087,6 +3389,12 @@
       <c r="BA41" s="0"/>
       <c r="BB41" s="0"/>
       <c r="BC41" s="0"/>
+      <c r="BD41" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE41" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
@@ -4152,6 +3460,12 @@
       <c r="BA42" s="0"/>
       <c r="BB42" s="0"/>
       <c r="BC42" s="0"/>
+      <c r="BD42" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE42" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
@@ -4217,6 +3531,12 @@
       <c r="BA43" s="0"/>
       <c r="BB43" s="0"/>
       <c r="BC43" s="0"/>
+      <c r="BD43" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE43" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
@@ -4282,6 +3602,12 @@
       <c r="BA44" s="0"/>
       <c r="BB44" s="0"/>
       <c r="BC44" s="0"/>
+      <c r="BD44" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE44" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
@@ -4347,6 +3673,12 @@
       <c r="BA45" s="0"/>
       <c r="BB45" s="0"/>
       <c r="BC45" s="0"/>
+      <c r="BD45" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE45" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
@@ -4412,6 +3744,12 @@
       <c r="BA46" s="0"/>
       <c r="BB46" s="0"/>
       <c r="BC46" s="0"/>
+      <c r="BD46" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE46" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
@@ -4477,6 +3815,12 @@
       <c r="BA47" s="0"/>
       <c r="BB47" s="0"/>
       <c r="BC47" s="0"/>
+      <c r="BD47" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE47" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
@@ -4542,6 +3886,12 @@
       <c r="BA48" s="0"/>
       <c r="BB48" s="0"/>
       <c r="BC48" s="0"/>
+      <c r="BD48" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE48" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
@@ -4607,6 +3957,12 @@
       <c r="BA49" s="0"/>
       <c r="BB49" s="0"/>
       <c r="BC49" s="0"/>
+      <c r="BD49" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE49" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
@@ -4672,6 +4028,12 @@
       <c r="BA50" s="0"/>
       <c r="BB50" s="0"/>
       <c r="BC50" s="0"/>
+      <c r="BD50" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE50" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
@@ -4737,6 +4099,12 @@
       <c r="BA51" s="0"/>
       <c r="BB51" s="0"/>
       <c r="BC51" s="0"/>
+      <c r="BD51" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE51" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
@@ -4802,6 +4170,12 @@
       <c r="BA52" s="0"/>
       <c r="BB52" s="0"/>
       <c r="BC52" s="0"/>
+      <c r="BD52" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE52" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
@@ -4867,6 +4241,12 @@
       <c r="BA53" s="0"/>
       <c r="BB53" s="0"/>
       <c r="BC53" s="0"/>
+      <c r="BD53" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE53" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
@@ -4932,6 +4312,12 @@
       <c r="BA54" s="0"/>
       <c r="BB54" s="0"/>
       <c r="BC54" s="0"/>
+      <c r="BD54" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE54" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
@@ -4997,6 +4383,12 @@
       <c r="BA55" s="0"/>
       <c r="BB55" s="0"/>
       <c r="BC55" s="0"/>
+      <c r="BD55" s="0">
+        <v>1</v>
+      </c>
+      <c r="BE55" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="s">
@@ -5062,6 +4454,12 @@
       <c r="BA56" s="0"/>
       <c r="BB56" s="0"/>
       <c r="BC56" s="0"/>
+      <c r="BD56" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE56" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="s">
@@ -5127,6 +4525,12 @@
       <c r="BA57" s="0"/>
       <c r="BB57" s="0"/>
       <c r="BC57" s="0"/>
+      <c r="BD57" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE57" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="s">
@@ -5192,6 +4596,12 @@
       <c r="BA58" s="0"/>
       <c r="BB58" s="0"/>
       <c r="BC58" s="0"/>
+      <c r="BD58" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE58" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
@@ -5257,6 +4667,12 @@
       <c r="BA59" s="0"/>
       <c r="BB59" s="0"/>
       <c r="BC59" s="0"/>
+      <c r="BD59" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE59" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="s">
@@ -5322,6 +4738,12 @@
       <c r="BA60" s="0"/>
       <c r="BB60" s="0"/>
       <c r="BC60" s="0"/>
+      <c r="BD60" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE60" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="s">
@@ -5387,6 +4809,12 @@
       <c r="BA61" s="0"/>
       <c r="BB61" s="0"/>
       <c r="BC61" s="0"/>
+      <c r="BD61" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE61" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="0" t="s">
@@ -5452,6 +4880,12 @@
       <c r="BA62" s="0"/>
       <c r="BB62" s="0"/>
       <c r="BC62" s="0"/>
+      <c r="BD62" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE62" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="0" t="s">
@@ -5517,6 +4951,12 @@
       <c r="BA63" s="0"/>
       <c r="BB63" s="0"/>
       <c r="BC63" s="0"/>
+      <c r="BD63" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE63" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="0" t="s">
@@ -5582,6 +5022,12 @@
       <c r="BA64" s="0"/>
       <c r="BB64" s="0"/>
       <c r="BC64" s="0"/>
+      <c r="BD64" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE64" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="0" t="s">
@@ -5647,6 +5093,12 @@
       <c r="BA65" s="0"/>
       <c r="BB65" s="0"/>
       <c r="BC65" s="0"/>
+      <c r="BD65" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE65" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="0" t="s">
@@ -5712,6 +5164,12 @@
       <c r="BA66" s="0"/>
       <c r="BB66" s="0"/>
       <c r="BC66" s="0"/>
+      <c r="BD66" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE66" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="0" t="s">
@@ -5777,6 +5235,12 @@
       <c r="BA67" s="0"/>
       <c r="BB67" s="0"/>
       <c r="BC67" s="0"/>
+      <c r="BD67" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE67" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="0" t="s">
@@ -5842,6 +5306,12 @@
       <c r="BA68" s="0"/>
       <c r="BB68" s="0"/>
       <c r="BC68" s="0"/>
+      <c r="BD68" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE68" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="0" t="s">
@@ -5907,6 +5377,12 @@
       <c r="BA69" s="0"/>
       <c r="BB69" s="0"/>
       <c r="BC69" s="0"/>
+      <c r="BD69" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE69" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="0" t="s">
@@ -5972,6 +5448,12 @@
       <c r="BA70" s="0"/>
       <c r="BB70" s="0"/>
       <c r="BC70" s="0"/>
+      <c r="BD70" s="0">
+        <v>1</v>
+      </c>
+      <c r="BE70" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="0" t="s">
@@ -6037,6 +5519,12 @@
       <c r="BA71" s="0"/>
       <c r="BB71" s="0"/>
       <c r="BC71" s="0"/>
+      <c r="BD71" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE71" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="0" t="s">
@@ -6102,6 +5590,12 @@
       <c r="BA72" s="0"/>
       <c r="BB72" s="0"/>
       <c r="BC72" s="0"/>
+      <c r="BD72" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE72" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="0" t="s">
@@ -6167,6 +5661,12 @@
       <c r="BA73" s="0"/>
       <c r="BB73" s="0"/>
       <c r="BC73" s="0"/>
+      <c r="BD73" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE73" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="0" t="s">
@@ -6232,6 +5732,12 @@
       <c r="BA74" s="0"/>
       <c r="BB74" s="0"/>
       <c r="BC74" s="0"/>
+      <c r="BD74" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE74" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="0" t="s">
@@ -6297,6 +5803,12 @@
       <c r="BA75" s="0"/>
       <c r="BB75" s="0"/>
       <c r="BC75" s="0"/>
+      <c r="BD75" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE75" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="0" t="s">
@@ -6362,6 +5874,12 @@
       <c r="BA76" s="0"/>
       <c r="BB76" s="0"/>
       <c r="BC76" s="0"/>
+      <c r="BD76" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE76" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="0" t="s">
@@ -6427,6 +5945,12 @@
       <c r="BA77" s="0"/>
       <c r="BB77" s="0"/>
       <c r="BC77" s="0"/>
+      <c r="BD77" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE77" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="0" t="s">
@@ -6492,6 +6016,12 @@
       <c r="BA78" s="0"/>
       <c r="BB78" s="0"/>
       <c r="BC78" s="0"/>
+      <c r="BD78" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE78" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="0" t="s">
@@ -6557,6 +6087,12 @@
       <c r="BA79" s="0"/>
       <c r="BB79" s="0"/>
       <c r="BC79" s="0"/>
+      <c r="BD79" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE79" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="0" t="s">
@@ -6622,6 +6158,12 @@
       <c r="BA80" s="0"/>
       <c r="BB80" s="0"/>
       <c r="BC80" s="0"/>
+      <c r="BD80" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE80" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="0" t="s">
@@ -6687,6 +6229,12 @@
       <c r="BA81" s="0"/>
       <c r="BB81" s="0"/>
       <c r="BC81" s="0"/>
+      <c r="BD81" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE81" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="0" t="s">
@@ -6752,6 +6300,12 @@
       <c r="BA82" s="0"/>
       <c r="BB82" s="0"/>
       <c r="BC82" s="0"/>
+      <c r="BD82" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE82" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="0" t="s">
@@ -6817,6 +6371,12 @@
       <c r="BA83" s="0"/>
       <c r="BB83" s="0"/>
       <c r="BC83" s="0"/>
+      <c r="BD83" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE83" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="0" t="s">
@@ -6882,6 +6442,12 @@
       <c r="BA84" s="0"/>
       <c r="BB84" s="0"/>
       <c r="BC84" s="0"/>
+      <c r="BD84" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE84" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="0" t="s">
@@ -6947,6 +6513,12 @@
       <c r="BA85" s="0"/>
       <c r="BB85" s="0"/>
       <c r="BC85" s="0"/>
+      <c r="BD85" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE85" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="0" t="s">
@@ -7012,6 +6584,12 @@
       <c r="BA86" s="0"/>
       <c r="BB86" s="0"/>
       <c r="BC86" s="0"/>
+      <c r="BD86" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE86" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="0" t="s">
@@ -7077,6 +6655,12 @@
       <c r="BA87" s="0"/>
       <c r="BB87" s="0"/>
       <c r="BC87" s="0"/>
+      <c r="BD87" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE87" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="0" t="s">
@@ -7142,6 +6726,12 @@
       <c r="BA88" s="0"/>
       <c r="BB88" s="0"/>
       <c r="BC88" s="0"/>
+      <c r="BD88" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE88" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="0" t="s">
@@ -7207,6 +6797,12 @@
       <c r="BA89" s="0"/>
       <c r="BB89" s="0"/>
       <c r="BC89" s="0"/>
+      <c r="BD89" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE89" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="0" t="s">
@@ -7272,6 +6868,12 @@
       <c r="BA90" s="0"/>
       <c r="BB90" s="0"/>
       <c r="BC90" s="0"/>
+      <c r="BD90" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE90" s="0">
+        <v>2</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="0" t="s">
@@ -7337,6 +6939,12 @@
       <c r="BA91" s="0"/>
       <c r="BB91" s="0"/>
       <c r="BC91" s="0"/>
+      <c r="BD91" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE91" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="0" t="s">
@@ -7402,6 +7010,12 @@
       <c r="BA92" s="0"/>
       <c r="BB92" s="0"/>
       <c r="BC92" s="0"/>
+      <c r="BD92" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE92" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="0" t="s">
@@ -7467,6 +7081,12 @@
       <c r="BA93" s="0"/>
       <c r="BB93" s="0"/>
       <c r="BC93" s="0"/>
+      <c r="BD93" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE93" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="0" t="s">
@@ -7532,6 +7152,12 @@
       <c r="BA94" s="0"/>
       <c r="BB94" s="0"/>
       <c r="BC94" s="0"/>
+      <c r="BD94" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE94" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="0" t="s">
@@ -7597,6 +7223,12 @@
       <c r="BA95" s="0"/>
       <c r="BB95" s="0"/>
       <c r="BC95" s="0"/>
+      <c r="BD95" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE95" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="0" t="s">
@@ -7662,6 +7294,12 @@
       <c r="BA96" s="0"/>
       <c r="BB96" s="0"/>
       <c r="BC96" s="0"/>
+      <c r="BD96" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE96" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="0" t="s">
@@ -7727,6 +7365,12 @@
       <c r="BA97" s="0"/>
       <c r="BB97" s="0"/>
       <c r="BC97" s="0"/>
+      <c r="BD97" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE97" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="0" t="s">
@@ -7792,6 +7436,12 @@
       <c r="BA98" s="0"/>
       <c r="BB98" s="0"/>
       <c r="BC98" s="0"/>
+      <c r="BD98" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE98" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="0" t="s">
@@ -7857,6 +7507,12 @@
       <c r="BA99" s="0"/>
       <c r="BB99" s="0"/>
       <c r="BC99" s="0"/>
+      <c r="BD99" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE99" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="0" t="s">
@@ -7922,6 +7578,12 @@
       <c r="BA100" s="0"/>
       <c r="BB100" s="0"/>
       <c r="BC100" s="0"/>
+      <c r="BD100" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE100" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="0" t="s">
@@ -7987,6 +7649,12 @@
       <c r="BA101" s="0"/>
       <c r="BB101" s="0"/>
       <c r="BC101" s="0"/>
+      <c r="BD101" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE101" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="0" t="s">
@@ -8052,6 +7720,12 @@
       <c r="BA102" s="0"/>
       <c r="BB102" s="0"/>
       <c r="BC102" s="0"/>
+      <c r="BD102" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE102" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="0" t="s">
@@ -8117,6 +7791,12 @@
       <c r="BA103" s="0"/>
       <c r="BB103" s="0"/>
       <c r="BC103" s="0"/>
+      <c r="BD103" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE103" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="0" t="s">
@@ -8182,6 +7862,12 @@
       <c r="BA104" s="0"/>
       <c r="BB104" s="0"/>
       <c r="BC104" s="0"/>
+      <c r="BD104" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE104" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="0" t="s">
@@ -8247,6 +7933,12 @@
       <c r="BA105" s="0"/>
       <c r="BB105" s="0"/>
       <c r="BC105" s="0"/>
+      <c r="BD105" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE105" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="0" t="s">
@@ -8312,6 +8004,12 @@
       <c r="BA106" s="0"/>
       <c r="BB106" s="0"/>
       <c r="BC106" s="0"/>
+      <c r="BD106" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE106" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="0" t="s">
@@ -8377,6 +8075,12 @@
       <c r="BA107" s="0"/>
       <c r="BB107" s="0"/>
       <c r="BC107" s="0"/>
+      <c r="BD107" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE107" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="0" t="s">
@@ -8442,6 +8146,12 @@
       <c r="BA108" s="0"/>
       <c r="BB108" s="0"/>
       <c r="BC108" s="0"/>
+      <c r="BD108" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE108" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="0" t="s">
@@ -8507,6 +8217,12 @@
       <c r="BA109" s="0"/>
       <c r="BB109" s="0"/>
       <c r="BC109" s="0"/>
+      <c r="BD109" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE109" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="0" t="s">
@@ -8572,6 +8288,12 @@
       <c r="BA110" s="0"/>
       <c r="BB110" s="0"/>
       <c r="BC110" s="0"/>
+      <c r="BD110" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE110" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="0" t="s">
@@ -8637,6 +8359,12 @@
       <c r="BA111" s="0"/>
       <c r="BB111" s="0"/>
       <c r="BC111" s="0"/>
+      <c r="BD111" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE111" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="0" t="s">
@@ -8702,6 +8430,12 @@
       <c r="BA112" s="0"/>
       <c r="BB112" s="0"/>
       <c r="BC112" s="0"/>
+      <c r="BD112" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE112" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="0" t="s">
@@ -8767,6 +8501,12 @@
       <c r="BA113" s="0"/>
       <c r="BB113" s="0"/>
       <c r="BC113" s="0"/>
+      <c r="BD113" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE113" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="0" t="s">
@@ -8832,6 +8572,12 @@
       <c r="BA114" s="0"/>
       <c r="BB114" s="0"/>
       <c r="BC114" s="0"/>
+      <c r="BD114" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE114" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="0" t="s">
@@ -8897,6 +8643,12 @@
       <c r="BA115" s="0"/>
       <c r="BB115" s="0"/>
       <c r="BC115" s="0"/>
+      <c r="BD115" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE115" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="0" t="s">
@@ -8962,6 +8714,12 @@
       <c r="BA116" s="0"/>
       <c r="BB116" s="0"/>
       <c r="BC116" s="0"/>
+      <c r="BD116" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE116" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="0" t="s">
@@ -9027,6 +8785,12 @@
       <c r="BA117" s="0"/>
       <c r="BB117" s="0"/>
       <c r="BC117" s="0"/>
+      <c r="BD117" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE117" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="0" t="s">
@@ -9092,6 +8856,12 @@
       <c r="BA118" s="0"/>
       <c r="BB118" s="0"/>
       <c r="BC118" s="0"/>
+      <c r="BD118" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE118" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="0" t="s">
@@ -9157,6 +8927,12 @@
       <c r="BA119" s="0"/>
       <c r="BB119" s="0"/>
       <c r="BC119" s="0"/>
+      <c r="BD119" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE119" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="0" t="s">
@@ -9222,6 +8998,12 @@
       <c r="BA120" s="0"/>
       <c r="BB120" s="0"/>
       <c r="BC120" s="0"/>
+      <c r="BD120" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE120" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="0" t="s">
@@ -9287,6 +9069,12 @@
       <c r="BA121" s="0"/>
       <c r="BB121" s="0"/>
       <c r="BC121" s="0"/>
+      <c r="BD121" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE121" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="0" t="s">
@@ -9352,6 +9140,12 @@
       <c r="BA122" s="0"/>
       <c r="BB122" s="0"/>
       <c r="BC122" s="0"/>
+      <c r="BD122" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE122" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="0" t="s">
@@ -9417,6 +9211,12 @@
       <c r="BA123" s="0"/>
       <c r="BB123" s="0"/>
       <c r="BC123" s="0"/>
+      <c r="BD123" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE123" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="0" t="s">
@@ -9482,6 +9282,12 @@
       <c r="BA124" s="0"/>
       <c r="BB124" s="0"/>
       <c r="BC124" s="0"/>
+      <c r="BD124" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE124" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="0" t="s">
@@ -9547,6 +9353,12 @@
       <c r="BA125" s="0"/>
       <c r="BB125" s="0"/>
       <c r="BC125" s="0"/>
+      <c r="BD125" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE125" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="0" t="s">
@@ -9612,6 +9424,12 @@
       <c r="BA126" s="0"/>
       <c r="BB126" s="0"/>
       <c r="BC126" s="0"/>
+      <c r="BD126" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE126" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="0" t="s">
@@ -9677,6 +9495,12 @@
       <c r="BA127" s="0"/>
       <c r="BB127" s="0"/>
       <c r="BC127" s="0"/>
+      <c r="BD127" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE127" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="0" t="s">
@@ -9742,6 +9566,12 @@
       <c r="BA128" s="0"/>
       <c r="BB128" s="0"/>
       <c r="BC128" s="0"/>
+      <c r="BD128" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE128" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="0" t="s">
@@ -9807,6 +9637,12 @@
       <c r="BA129" s="0"/>
       <c r="BB129" s="0"/>
       <c r="BC129" s="0"/>
+      <c r="BD129" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE129" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="0" t="s">
@@ -9872,6 +9708,12 @@
       <c r="BA130" s="0"/>
       <c r="BB130" s="0"/>
       <c r="BC130" s="0"/>
+      <c r="BD130" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE130" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="0" t="s">
@@ -9937,6 +9779,12 @@
       <c r="BA131" s="0"/>
       <c r="BB131" s="0"/>
       <c r="BC131" s="0"/>
+      <c r="BD131" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE131" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="0" t="s">
@@ -10002,6 +9850,12 @@
       <c r="BA132" s="0"/>
       <c r="BB132" s="0"/>
       <c r="BC132" s="0"/>
+      <c r="BD132" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE132" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="0" t="s">
@@ -10067,6 +9921,12 @@
       <c r="BA133" s="0"/>
       <c r="BB133" s="0"/>
       <c r="BC133" s="0"/>
+      <c r="BD133" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE133" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="0" t="s">
@@ -10132,6 +9992,12 @@
       <c r="BA134" s="0"/>
       <c r="BB134" s="0"/>
       <c r="BC134" s="0"/>
+      <c r="BD134" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE134" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="0" t="s">
@@ -10197,6 +10063,12 @@
       <c r="BA135" s="0"/>
       <c r="BB135" s="0"/>
       <c r="BC135" s="0"/>
+      <c r="BD135" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE135" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="0" t="s">
@@ -10262,6 +10134,12 @@
       <c r="BA136" s="0"/>
       <c r="BB136" s="0"/>
       <c r="BC136" s="0"/>
+      <c r="BD136" s="0">
+        <v>1</v>
+      </c>
+      <c r="BE136" s="0">
+        <v>1</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="0" t="s">
@@ -10327,6 +10205,12 @@
       <c r="BA137" s="0"/>
       <c r="BB137" s="0"/>
       <c r="BC137" s="0"/>
+      <c r="BD137" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE137" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="0" t="s">
@@ -10392,6 +10276,12 @@
       <c r="BA138" s="0"/>
       <c r="BB138" s="0"/>
       <c r="BC138" s="0"/>
+      <c r="BD138" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE138" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="0" t="s">
@@ -10457,6 +10347,12 @@
       <c r="BA139" s="0"/>
       <c r="BB139" s="0"/>
       <c r="BC139" s="0"/>
+      <c r="BD139" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE139" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="0" t="s">
@@ -10522,6 +10418,12 @@
       <c r="BA140" s="0"/>
       <c r="BB140" s="0"/>
       <c r="BC140" s="0"/>
+      <c r="BD140" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE140" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="0" t="s">
@@ -10587,6 +10489,12 @@
       <c r="BA141" s="0"/>
       <c r="BB141" s="0"/>
       <c r="BC141" s="0"/>
+      <c r="BD141" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE141" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="0" t="s">
@@ -10652,6 +10560,12 @@
       <c r="BA142" s="0"/>
       <c r="BB142" s="0"/>
       <c r="BC142" s="0"/>
+      <c r="BD142" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE142" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="0" t="s">
@@ -10717,6 +10631,12 @@
       <c r="BA143" s="0"/>
       <c r="BB143" s="0"/>
       <c r="BC143" s="0"/>
+      <c r="BD143" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE143" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="0" t="s">
@@ -10782,6 +10702,12 @@
       <c r="BA144" s="0"/>
       <c r="BB144" s="0"/>
       <c r="BC144" s="0"/>
+      <c r="BD144" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE144" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="0" t="s">
@@ -10847,6 +10773,12 @@
       <c r="BA145" s="0"/>
       <c r="BB145" s="0"/>
       <c r="BC145" s="0"/>
+      <c r="BD145" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE145" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="0" t="s">
@@ -10912,6 +10844,12 @@
       <c r="BA146" s="0"/>
       <c r="BB146" s="0"/>
       <c r="BC146" s="0"/>
+      <c r="BD146" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE146" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="0" t="s">
@@ -10977,6 +10915,12 @@
       <c r="BA147" s="0"/>
       <c r="BB147" s="0"/>
       <c r="BC147" s="0"/>
+      <c r="BD147" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE147" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="0" t="s">
@@ -11042,6 +10986,12 @@
       <c r="BA148" s="0"/>
       <c r="BB148" s="0"/>
       <c r="BC148" s="0"/>
+      <c r="BD148" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE148" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="0" t="s">
@@ -11107,6 +11057,12 @@
       <c r="BA149" s="0"/>
       <c r="BB149" s="0"/>
       <c r="BC149" s="0"/>
+      <c r="BD149" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE149" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="0" t="s">
@@ -11172,6 +11128,12 @@
       <c r="BA150" s="0"/>
       <c r="BB150" s="0"/>
       <c r="BC150" s="0"/>
+      <c r="BD150" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE150" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="0" t="s">
@@ -11237,6 +11199,12 @@
       <c r="BA151" s="0"/>
       <c r="BB151" s="0"/>
       <c r="BC151" s="0"/>
+      <c r="BD151" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE151" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="0" t="s">
@@ -11302,6 +11270,12 @@
       <c r="BA152" s="0"/>
       <c r="BB152" s="0"/>
       <c r="BC152" s="0"/>
+      <c r="BD152" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE152" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="0" t="s">
@@ -11367,6 +11341,12 @@
       <c r="BA153" s="0"/>
       <c r="BB153" s="0"/>
       <c r="BC153" s="0"/>
+      <c r="BD153" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE153" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="0" t="s">
@@ -11432,6 +11412,12 @@
       <c r="BA154" s="0"/>
       <c r="BB154" s="0"/>
       <c r="BC154" s="0"/>
+      <c r="BD154" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE154" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="0" t="s">
@@ -11497,6 +11483,12 @@
       <c r="BA155" s="0"/>
       <c r="BB155" s="0"/>
       <c r="BC155" s="0"/>
+      <c r="BD155" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE155" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="0" t="s">
@@ -11562,6 +11554,12 @@
       <c r="BA156" s="0"/>
       <c r="BB156" s="0"/>
       <c r="BC156" s="0"/>
+      <c r="BD156" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE156" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="0" t="s">
@@ -11627,6 +11625,12 @@
       <c r="BA157" s="0"/>
       <c r="BB157" s="0"/>
       <c r="BC157" s="0"/>
+      <c r="BD157" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE157" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="0" t="s">
@@ -11692,6 +11696,12 @@
       <c r="BA158" s="0"/>
       <c r="BB158" s="0"/>
       <c r="BC158" s="0"/>
+      <c r="BD158" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE158" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="0" t="s">
@@ -11757,6 +11767,12 @@
       <c r="BA159" s="0"/>
       <c r="BB159" s="0"/>
       <c r="BC159" s="0"/>
+      <c r="BD159" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE159" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="0" t="s">
@@ -11822,6 +11838,12 @@
       <c r="BA160" s="0"/>
       <c r="BB160" s="0"/>
       <c r="BC160" s="0"/>
+      <c r="BD160" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE160" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="0" t="s">
@@ -11887,6 +11909,12 @@
       <c r="BA161" s="0"/>
       <c r="BB161" s="0"/>
       <c r="BC161" s="0"/>
+      <c r="BD161" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE161" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="0" t="s">
@@ -11952,6 +11980,12 @@
       <c r="BA162" s="0"/>
       <c r="BB162" s="0"/>
       <c r="BC162" s="0"/>
+      <c r="BD162" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE162" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="0" t="s">
@@ -12017,6 +12051,12 @@
       <c r="BA163" s="0"/>
       <c r="BB163" s="0"/>
       <c r="BC163" s="0"/>
+      <c r="BD163" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE163" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="0" t="s">
@@ -12082,6 +12122,12 @@
       <c r="BA164" s="0"/>
       <c r="BB164" s="0"/>
       <c r="BC164" s="0"/>
+      <c r="BD164" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE164" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="0" t="s">
@@ -12147,6 +12193,12 @@
       <c r="BA165" s="0"/>
       <c r="BB165" s="0"/>
       <c r="BC165" s="0"/>
+      <c r="BD165" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE165" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="0" t="s">
@@ -12212,6 +12264,12 @@
       <c r="BA166" s="0"/>
       <c r="BB166" s="0"/>
       <c r="BC166" s="0"/>
+      <c r="BD166" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE166" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="0" t="s">
@@ -12277,6 +12335,12 @@
       <c r="BA167" s="0"/>
       <c r="BB167" s="0"/>
       <c r="BC167" s="0"/>
+      <c r="BD167" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE167" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="0" t="s">
@@ -12342,6 +12406,12 @@
       <c r="BA168" s="0"/>
       <c r="BB168" s="0"/>
       <c r="BC168" s="0"/>
+      <c r="BD168" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE168" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="0" t="s">
@@ -12407,6 +12477,12 @@
       <c r="BA169" s="0"/>
       <c r="BB169" s="0"/>
       <c r="BC169" s="0"/>
+      <c r="BD169" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE169" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="0" t="s">
@@ -12472,6 +12548,12 @@
       <c r="BA170" s="0"/>
       <c r="BB170" s="0"/>
       <c r="BC170" s="0"/>
+      <c r="BD170" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE170" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="0" t="s">
@@ -12537,6 +12619,12 @@
       <c r="BA171" s="0"/>
       <c r="BB171" s="0"/>
       <c r="BC171" s="0"/>
+      <c r="BD171" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE171" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="0" t="s">
@@ -12602,6 +12690,12 @@
       <c r="BA172" s="0"/>
       <c r="BB172" s="0"/>
       <c r="BC172" s="0"/>
+      <c r="BD172" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE172" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="0" t="s">
@@ -12667,6 +12761,12 @@
       <c r="BA173" s="0"/>
       <c r="BB173" s="0"/>
       <c r="BC173" s="0"/>
+      <c r="BD173" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE173" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="0" t="s">
@@ -12732,6 +12832,12 @@
       <c r="BA174" s="0"/>
       <c r="BB174" s="0"/>
       <c r="BC174" s="0"/>
+      <c r="BD174" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE174" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="0" t="s">
@@ -12797,6 +12903,12 @@
       <c r="BA175" s="0"/>
       <c r="BB175" s="0"/>
       <c r="BC175" s="0"/>
+      <c r="BD175" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE175" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="0" t="s">
@@ -12862,6 +12974,12 @@
       <c r="BA176" s="0"/>
       <c r="BB176" s="0"/>
       <c r="BC176" s="0"/>
+      <c r="BD176" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE176" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="0" t="s">
@@ -12927,6 +13045,12 @@
       <c r="BA177" s="0"/>
       <c r="BB177" s="0"/>
       <c r="BC177" s="0"/>
+      <c r="BD177" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE177" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="0" t="s">
@@ -12992,6 +13116,12 @@
       <c r="BA178" s="0"/>
       <c r="BB178" s="0"/>
       <c r="BC178" s="0"/>
+      <c r="BD178" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE178" s="0">
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="0" t="s">
@@ -13057,6 +13187,12 @@
       <c r="BA179" s="0"/>
       <c r="BB179" s="0"/>
       <c r="BC179" s="0"/>
+      <c r="BD179" s="0">
+        <v>0</v>
+      </c>
+      <c r="BE179" s="0">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
 </worksheet>
